--- a/data/outputs/ml_analysis_results.xlsx
+++ b/data/outputs/ml_analysis_results.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="146">
   <si>
     <t>Feature Set</t>
   </si>
@@ -42,15 +42,15 @@
     <t>extended</t>
   </si>
   <si>
+    <t>Linear Regression</t>
+  </si>
+  <si>
     <t>Random Forest</t>
   </si>
   <si>
     <t>Decision Tree</t>
   </si>
   <si>
-    <t>Linear Regression</t>
-  </si>
-  <si>
     <t>Source</t>
   </si>
   <si>
@@ -99,19 +99,22 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>Furnished</t>
+  </si>
+  <si>
     <t>Unfurnished</t>
   </si>
   <si>
-    <t>Furnished</t>
-  </si>
-  <si>
     <t>16-20 Years</t>
   </si>
   <si>
+    <t>11-15 Years</t>
+  </si>
+  <si>
     <t>6-10 Years</t>
   </si>
   <si>
-    <t>11-15 Years</t>
+    <t>21+ Years</t>
   </si>
   <si>
     <t>0-5 Years</t>
@@ -120,64 +123,328 @@
     <t>https://www.emlakjet.com/ilan/kurkoyde-kiralik-31-daire-ev-sahibinden-detay-icin-bu-numarayi-arayin-o534-968-91-35-18514905</t>
   </si>
   <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-de-merkez-de-4-plus2-30m2-terasli-kiralik-dubleks-1275995823/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-al-grup-r.kaya-dan-kurtkoy-merkezde-kiralik-kelepir-daire-1268637928/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-kiralik-daire-1283728638/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-kiralik-3-plus1-daire-1285418956/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-kiralik-giris-kat-daire-1284178037/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-ara-kat-aile-binasi-2-plus1-kiralik-daire-1279559891/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkez-de-sahibinden-3-plus1-esyali-1284613505/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kacmaz-emlak-cagri-koc-tan-kelepir-daire-1280271775/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurkoy-merkez-de-kiralik-cok-genis-3-plus1-daire-1283885468/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkkezde-kiralik-daire-1277019116/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-academy-pendik-kurtkoy-genc-binada-kiralik-3-plus1-1284456017/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/58790-288</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-metronun-yanibasinda-kiralik-3-plus1-genis-tip-arakat-1281048082/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy___merkezde___genis___kiralik___daire-1281297299/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kececi-den-pendik-kurtoy-den-kiralik-daire-1280817122/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkeze-yakin-kiralik-2-plus-1-daire-1275550294/detay</t>
+  </si>
+  <si>
     <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kececi-den-pendik-kurtkoy-merkezden-kiralik-3-plus1-daire-1285842162/detay</t>
   </si>
   <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/123393-103</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-selcuk-emlaktan-cadde-ustu-site-ici-ara-kat-3-plus1-kiralik-1284103821/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-evtas-havuzlu-sitede-guvenlikli-kapali-otoparkli-arakat-1283762137/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-3-plus1-kiralik-daire-1154145444/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-otoparkli-genis-onu-acik-3-plus1-kiralik-1284658888/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-pendik-kurtkoy-ibb-mesken-konutlarinda-bos-2-plus1-kiralik-daire-1273685489/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-site-icinde-3-plus1-dubleks-1266966691/detay</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/pendik-kurtkoy-ibb-mesken-konutlarinda-bos-21-kiralik-daire-18150125</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-metro-yani-3-plus1-daire-1285674663/detay</t>
+  </si>
+  <si>
     <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/123393-98</t>
   </si>
   <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-palmiye-sitesinde-yenilenmis-kiralik-3-plus1-daire-1279602577/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kiralik-2-plus1-ibb-mesken-konutlari-safa-caddesi-uzerinde-1280461072/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-kugu-park-sitesinde-3-plus1-kiralik-daire-1274516084/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-kiralik-2-plus1-daire-metronun-dibinde-1279727707/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-teknopark-cevresi-esyali-2-plus1-daire-kiraliktir-1279406359/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-pendik-kurtkoy-80m2-kapali-mutfakli-balkonlu-kiralik-2-plus1-daire-1277774820/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/162096-23</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-metroya-komsu-4-yasinda-85-m-net-balkonlu-ferah-2-plus1-1284959950/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-de-metroya-ve-sabiha-gokcene-5dk-yakinlikta-10-numara-1282019191/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kiralikkk-2-plus1-guney-cephe-90-m2-k.otoparkli-1281817002/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-aile-binasi-dogalgazli-cift-balkonlu-gayet-genis-bir-daire-1283866305/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/159543-29</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/mertcan-dan-metroya-1dk-yurume-mesafeli-ara-kat-balkonlu-21-18504927</t>
+  </si>
+  <si>
     <t>https://www.emlakjet.com/ilan/mertcan-dan-kurtkoy-mesken-bloklarinda-balkonlu-esyali-21-18499579</t>
   </si>
   <si>
-    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-kiralik-2-plus1-daire-metronun-dibinde-1279727707/detay</t>
-  </si>
-  <si>
-    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-pendik-kurtkoy-ibb-mesken-konutlarinda-bos-2-plus1-kiralik-daire-1273685489/detay</t>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/136086-27</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-al-grup-tan-havaalanina-komsu-turna-life-sitesinde-2-plus1-kiralik-1282852842/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kacmaz-emlak-tan-metroya-havalimanina-yakin-genis-3-plus-1-daire-1278907540/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-ibb-mesken-konutlari-kiralik-2-plus1-daire-1284544537/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-by-vista-sitesinde-brut-85-m-2-plus1-kiralik-daire-1275711416/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-by-vista-sitesinde-1-plus1-kiralik-bos-daire-havuz-cephe-1284126986/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-tek-yetkili-kurtkoy-metro-yakini-by-vista-sitesi-havuz-cepheli-1275691668/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-aile-yasamina-uygun-3-plus1-kiralik-daire-1282585500/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/133645-17</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-de-kiralik-dublex-3-plus1-daire-1283425375/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kacmaz-emlak-cagri-koc-tan-site-icerisinde-daire-1275720443/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-alkanlar-emlak-pendik-kurtkoy-merkez-de-kiralik-daire-2-plus1-bos-1285087982/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/133645-32</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/162096-10</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-sapphire-hill-sitesi-esyali-1-plus1-kiralik-daire-metro-15dk-1285834899/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-mesken-konutlari-2-plus1-kiralik-daire-1279474633/detay</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/sabihagokcen-havaalani-karsisi-lunaport-sitesi-21-kiralik-daire-18727397</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-kiralik-2-plus1-daire-1282809091/detay</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/kurtkoy-de-butik-korkmazkaya-sitesinde-kiralik-21-daire-18563087</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-metrosuna-komsu-ersoy-hastanesine-paralel-1280407921/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/162096-29</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-al-grup-tan-kurtkoy-merkezde-kiralik-2-plus1-daire-1283100186/detay</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/sabiha-gokcen-havaalani-karsisinda-kiralik-21-daire-18478661</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-cenk-atalay-solak-tan-yeni-bina-da-2-plus1-kiralik-ankastreli-daire-1276227776/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/122389-1004</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-ozyapi-dan-kurtkoy-de-metroya-2-dk-mesafe-de-kiralik-1-plus1-daire-1283361838/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-satis-ofisinden-loca-evlerin-de-kiralik-1-plus1-havuz-cephe-daire-1286036091/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/0-45814162</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkezde-yeni-binada-2-plus1-kiralik-daire-metro-10-dk-1283831397/detay</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/mertcan-dan-firsat-emsey-has-karsisi-terasli-11-kiralik-daire-18721071</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-loca-sitesinde-bos-1-plus1-daire-1269604799/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-7tepeden-kurtkoy-by-vista-da-kiralik-4-kat-80m2-daire-1276125307/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-merkez-de-kiralik-2-plus1-genis-ferah-daire-1277274952/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-pendik-kurtkoy-sekerevler-sitesinde-3-plus1-kiralik-daire-1270987653/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kiralik-daire-metroya-yakin-ara-kat-daire-1281620405/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-silkroad-residence-havuz-cephe-balkonlu-81m2-kiralik-1-plus1-daire-1267088280/detay</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/kurtkoy-loca-sitesinde-bos-11-daire-18197569</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-manzarali-sakin-merkezi-yeni-ve-temiz-2-plus1-sahibinden-kiralik-1283400851/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-vogue-kurtkoy-deki-komsunuzdan-kiralik-1-plus1-daire-oturuma-hazir-1285461174/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-pendik-kurtkoy-de-sabiha-gokcene-yakin-kiralik-2-plus1-daire-1268304177/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-sabiha-gokcen-havaalani-karsisinda-kiralik-2-plus1-daire-1283029587/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-minik-emlak-tan-kurtkoy-merkezde-ankastreli-2-plus1-1272788710/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-nokta-dan-kurtkoy-metro-yakini-loca-evlerinde-2-plus1-kiralik-daire-1285884360/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-konut-atolyesi-by-vista-1-plus1-aralik-teslim-1284486013/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-mertcan-dan-emsey-hastanesi-yurume-9dk-balkonlu-ara-kat-2-plus1-1284350873/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-sahibinden-kiralik-3-plus1-daire-1281428529/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/161261-259</t>
   </si>
   <si>
     <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/42003-7068</t>
   </si>
   <si>
-    <t>https://www.emlakjet.com/ilan/pendik-kurtkoy-kiralik-10-18436170</t>
-  </si>
-  <si>
-    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-satis-ofisinden-loca-evlerin-de-kiralik-1-plus1-havuz-cephe-daire-1286036091/detay</t>
-  </si>
-  <si>
-    <t>https://www.emlakjet.com/ilan/pendik-kurtkoy-ibb-mesken-konutlarinda-bos-21-kiralik-daire-18150125</t>
-  </si>
-  <si>
-    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/162096-23</t>
-  </si>
-  <si>
-    <t>https://www.emlakjet.com/ilan/mertcan-dan-metroya-1dk-yurume-mesafeli-ara-kat-balkonlu-21-18504927</t>
-  </si>
-  <si>
-    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/122389-1004</t>
-  </si>
-  <si>
-    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-sapphire-hill-sitesi-esyali-1-plus1-kiralik-daire-metro-15dk-1285834899/detay</t>
-  </si>
-  <si>
-    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-nokta-dan-kurtkoy-metro-yakini-loca-evlerinde-2-plus1-kiralik-daire-1285884360/detay</t>
+    <t>https://www.emlakjet.com/ilan/cenk-atalay-solak-tan-yeni-bina-da-21-kiralik-ankastreli-daire-18231514</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/mertcan-dan-emsey-hastanesi-yurume-9dk-balkonlu-ara-kat-21-18499795</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/havaalani-bes-dakika-kurtkoy-merkezde-11-kiralik-daire-18613913</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-alkanlar-emlaktan-kurtkoy-merkezde-kiralik-bos-daire-1276011540/detay</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/mertcan-dan-emsey-hastanesi-yurume-9dk-balkonlu-ara-kat-21-18658871</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-minik-emlak-tan-merkezi-konumda-2-plus1-1273343120/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-minik-emlak-tan-kurtkoy-de-genis-1-plus1-daire-1244626280/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kacmaz-emlak-cagri-koc-tan-kullanisli-daire-1285309299/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-var-merkeze-5-dk-uzaklikta-21-daire-acik-otopark-doga-sb2f-lux-846781237/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/123393-86</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-optimum-yenisehir-projesinde-sifir-1-plus1-kiralik-arakat-daire-1275413652/detay</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/3m-yapi-dan-pendik-mesken-sitesinde-geniis-kiralik-21-daire-18600661</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-optimum-yenisehir-sitesin-de-1-plus1-kiralik-daire-1268706853/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-optimum-yenisehir-projesinde-2-plus1-acik-mutfakli-kiralik-daire-1265555588/detay</t>
+  </si>
+  <si>
+    <t>https://www.emlakjet.com/ilan/kurtkoy-de-havuzlu-luks-sitede-esyali-11-18577037</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-kurtkoy-metroya-3-dk-1-plus1-minubus-yolu-uzeri-kiralik-1262138346/detay</t>
+  </si>
+  <si>
+    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-sadece-kurumsal-calisana-optimum-yenisehir-sifir-1-plus1-kiralik-1285210874/detay</t>
+  </si>
+  <si>
+    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/33208-5751</t>
   </si>
   <si>
     <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/162096-49</t>
-  </si>
-  <si>
-    <t>https://www.emlakjet.com/ilan/cenk-atalay-solak-tan-yeni-bina-da-21-kiralik-ankastreli-daire-18231514</t>
-  </si>
-  <si>
-    <t>https://www.emlakjet.com/ilan/kurtkoy-loca-sitesinde-bos-11-daire-18197569</t>
-  </si>
-  <si>
-    <t>https://www.hepsiemlak.com/istanbul-pendik-kurtkoy-kiralik/daire/162096-29</t>
-  </si>
-  <si>
-    <t>https://www.emlakjet.com/ilan/5-katli-binada-sabiha-gokcen-e-5-dakika-mesafede-kiralik-daire-18027500</t>
-  </si>
-  <si>
-    <t>https://www.sahibinden.com/ilan/emlak-konut-kiralik-pendik-kurtkoy-de-kiralik-ust-kat-2-plus1-daire-1273605053/detay</t>
   </si>
   <si>
     <t>Price</t>
@@ -588,16 +855,16 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>0.2283783193261963</v>
+        <v>0.2494991294124607</v>
       </c>
       <c r="D2">
-        <v>0.2441517838106589</v>
+        <v>0.1088685864870249</v>
       </c>
       <c r="E2">
-        <v>4252.760848248283</v>
+        <v>4930.043489704863</v>
       </c>
       <c r="F2">
-        <v>5889.943339982922</v>
+        <v>6502.592628628717</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -608,16 +875,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0.1616174330206818</v>
+        <v>0.2048280442707129</v>
       </c>
       <c r="D3">
-        <v>0.1639032348581513</v>
+        <v>0.1356686162404668</v>
       </c>
       <c r="E3">
-        <v>4514.76552154393</v>
+        <v>5062.93487572778</v>
       </c>
       <c r="F3">
-        <v>6266.519549191897</v>
+        <v>6683.058364380838</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -628,56 +895,56 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>0.1166421420426259</v>
+        <v>0.1997158152412702</v>
       </c>
       <c r="D4">
-        <v>0.2857521788236643</v>
+        <v>0.1178083632079679</v>
       </c>
       <c r="E4">
-        <v>4683.590111986124</v>
+        <v>4818.392152496336</v>
       </c>
       <c r="F4">
-        <v>6211.234754971408</v>
+        <v>6761.379598425005</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>-0.03508975395847902</v>
+        <v>0.1984853274632044</v>
       </c>
       <c r="D5">
-        <v>0.5648694986975291</v>
+        <v>0.1175056415134307</v>
       </c>
       <c r="E5">
-        <v>4895.858414234509</v>
+        <v>4803.746014978879</v>
       </c>
       <c r="F5">
-        <v>6350.882832408806</v>
+        <v>6764.737137848019</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>-0.06779539861016937</v>
+        <v>0.1375808496141143</v>
       </c>
       <c r="D6">
-        <v>0.2554143079691579</v>
+        <v>0.08967698674159538</v>
       </c>
       <c r="E6">
-        <v>5068.009352656553</v>
+        <v>5061.593125346497</v>
       </c>
       <c r="F6">
-        <v>6965.024230668706</v>
+        <v>7047.269373322</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -688,16 +955,16 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>-1.561950485336481</v>
+        <v>0.1293210035124566</v>
       </c>
       <c r="D7">
-        <v>3.243569613283068</v>
+        <v>0.07538286469999524</v>
       </c>
       <c r="E7">
-        <v>5988.028765030619</v>
+        <v>5091.522493401368</v>
       </c>
       <c r="F7">
-        <v>8678.669157793711</v>
+        <v>7069.202790513207</v>
       </c>
     </row>
   </sheetData>
@@ -707,7 +974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -756,10 +1023,10 @@
         <v>21000</v>
       </c>
       <c r="C2">
-        <v>35436.03078378076</v>
+        <v>39107.29681423494</v>
       </c>
       <c r="D2">
-        <v>14436.03078378076</v>
+        <v>18107.29681423494</v>
       </c>
       <c r="E2">
         <v>130</v>
@@ -777,10 +1044,10 @@
         <v>26</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -788,57 +1055,54 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>32000</v>
+        <v>47000</v>
       </c>
       <c r="C3">
-        <v>41723.51312325797</v>
+        <v>60418.19047287447</v>
       </c>
       <c r="D3">
-        <v>9723.513123257966</v>
+        <v>13418.19047287447</v>
       </c>
       <c r="E3">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>26500</v>
+        <v>19500</v>
       </c>
       <c r="C4">
-        <v>35004.10840578416</v>
+        <v>32647.00117439831</v>
       </c>
       <c r="D4">
-        <v>8504.108405784158</v>
+        <v>13147.00117439831</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -847,33 +1111,30 @@
         <v>2</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="C5">
-        <v>36973.6968988137</v>
+        <v>32647.00117439831</v>
       </c>
       <c r="D5">
-        <v>6973.696898813701</v>
+        <v>12647.00117439831</v>
       </c>
       <c r="E5">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -882,7 +1143,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -890,34 +1151,31 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="C6">
-        <v>35050.0400758218</v>
+        <v>40280.72280121865</v>
       </c>
       <c r="D6">
-        <v>5050.040075821802</v>
+        <v>12280.72280121865</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -925,57 +1183,54 @@
         <v>24</v>
       </c>
       <c r="B7">
-        <v>25500</v>
+        <v>20000</v>
       </c>
       <c r="C7">
-        <v>29675.44523411059</v>
+        <v>31700.46839765928</v>
       </c>
       <c r="D7">
-        <v>4175.445234110586</v>
+        <v>11700.46839765928</v>
       </c>
       <c r="E7">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J7">
         <v>2</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>32000</v>
+        <v>21000</v>
       </c>
       <c r="C8">
-        <v>35843.36486889944</v>
+        <v>32026.28129083755</v>
       </c>
       <c r="D8">
-        <v>3843.364868899436</v>
+        <v>11026.28129083755</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -984,30 +1239,27 @@
         <v>2</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>24500</v>
+        <v>32500</v>
       </c>
       <c r="C9">
-        <v>28132.06478357099</v>
+        <v>42780.80107181189</v>
       </c>
       <c r="D9">
-        <v>3632.06478357099</v>
+        <v>10280.80107181189</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" t="s">
         <v>27</v>
@@ -1016,10 +1268,10 @@
         <v>26</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1027,124 +1279,115 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="C10">
-        <v>28376.95655046414</v>
+        <v>32021.26190001904</v>
       </c>
       <c r="D10">
-        <v>3376.956550464143</v>
+        <v>10021.26190001904</v>
       </c>
       <c r="E10">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
-        <v>26000</v>
+        <v>28750</v>
       </c>
       <c r="C11">
-        <v>29316.97515154854</v>
+        <v>38581.63391397151</v>
       </c>
       <c r="D11">
-        <v>3316.975151548544</v>
+        <v>9831.633913971506</v>
       </c>
       <c r="E11">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="C12">
-        <v>28284.71415573652</v>
+        <v>32784.73587343442</v>
       </c>
       <c r="D12">
-        <v>3284.714155736525</v>
+        <v>9784.735873434423</v>
       </c>
       <c r="E12">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>26750</v>
+        <v>28500</v>
       </c>
       <c r="C13">
-        <v>29911.74146064377</v>
+        <v>38184.56384637089</v>
       </c>
       <c r="D13">
-        <v>3161.741460643774</v>
+        <v>9684.563846370889</v>
       </c>
       <c r="E13">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13" t="s">
         <v>26</v>
@@ -1153,10 +1396,10 @@
         <v>26</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1164,31 +1407,34 @@
         <v>25</v>
       </c>
       <c r="B14">
-        <v>25500</v>
+        <v>30000</v>
       </c>
       <c r="C14">
-        <v>28473.49677116466</v>
+        <v>39153.66045948091</v>
       </c>
       <c r="D14">
-        <v>2973.49677116466</v>
+        <v>9153.660459480911</v>
       </c>
       <c r="E14">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I14" t="s">
         <v>26</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>8</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1196,34 +1442,31 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="C15">
-        <v>29738.8491064451</v>
+        <v>38581.63391397151</v>
       </c>
       <c r="D15">
-        <v>2738.849106445105</v>
+        <v>8581.633913971506</v>
       </c>
       <c r="E15">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1231,48 +1474,45 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>30500</v>
+        <v>24000</v>
       </c>
       <c r="C16">
-        <v>33161.18165222726</v>
+        <v>32324.49444767221</v>
       </c>
       <c r="D16">
-        <v>2661.181652227257</v>
+        <v>8324.494447672212</v>
       </c>
       <c r="E16">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
       <c r="H16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J16">
         <v>2</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17">
-        <v>32000</v>
+        <v>24000</v>
       </c>
       <c r="C17">
-        <v>33957.14454571767</v>
+        <v>32248.41816151449</v>
       </c>
       <c r="D17">
-        <v>1957.144545717674</v>
+        <v>8248.418161514488</v>
       </c>
       <c r="E17">
         <v>95</v>
@@ -1281,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
@@ -1290,77 +1530,74 @@
         <v>2</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18">
-        <v>31000</v>
+        <v>24000</v>
       </c>
       <c r="C18">
-        <v>32651.98815945445</v>
+        <v>32026.28129083755</v>
       </c>
       <c r="D18">
-        <v>1651.988159454446</v>
+        <v>8026.281290837545</v>
       </c>
       <c r="E18">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
       <c r="H18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
-        <v>25000</v>
+        <v>32000</v>
       </c>
       <c r="C19">
-        <v>26498.15628965187</v>
+        <v>39994.6267194756</v>
       </c>
       <c r="D19">
-        <v>1498.156289651874</v>
+        <v>7994.6267194756</v>
       </c>
       <c r="E19">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1368,19 +1605,19 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="C20">
-        <v>27916.24383356191</v>
+        <v>37891.47105822666</v>
       </c>
       <c r="D20">
-        <v>916.2438335619117</v>
+        <v>7891.471058226656</v>
       </c>
       <c r="E20">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" t="s">
         <v>28</v>
@@ -1389,48 +1626,42 @@
         <v>26</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
-        <v>33000</v>
+        <v>31000</v>
       </c>
       <c r="C21">
-        <v>33159.49336287343</v>
+        <v>38722.23051010666</v>
       </c>
       <c r="D21">
-        <v>159.4933628734289</v>
+        <v>7722.230510106659</v>
       </c>
       <c r="E21">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F21">
-        <v>3</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I21" t="s">
         <v>26</v>
       </c>
       <c r="J21">
-        <v>2</v>
-      </c>
-      <c r="K21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1438,34 +1669,2982 @@
         <v>24</v>
       </c>
       <c r="B22">
+        <v>30000</v>
+      </c>
+      <c r="C22">
+        <v>37556.22972723112</v>
+      </c>
+      <c r="D22">
+        <v>7556.229727231119</v>
+      </c>
+      <c r="E22">
+        <v>118</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <v>31000</v>
+      </c>
+      <c r="C23">
+        <v>38452.45744015665</v>
+      </c>
+      <c r="D23">
+        <v>7452.45744015665</v>
+      </c>
+      <c r="E23">
+        <v>110</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="H23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>31000</v>
+      </c>
+      <c r="C24">
+        <v>38452.45744015665</v>
+      </c>
+      <c r="D24">
+        <v>7452.45744015665</v>
+      </c>
+      <c r="E24">
+        <v>110</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="H24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>25500</v>
+      </c>
+      <c r="C25">
+        <v>32941.57952708909</v>
+      </c>
+      <c r="D25">
+        <v>7441.579527089089</v>
+      </c>
+      <c r="E25">
+        <v>105</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>33000</v>
+      </c>
+      <c r="C26">
+        <v>40049.48434309666</v>
+      </c>
+      <c r="D26">
+        <v>7049.484343096665</v>
+      </c>
+      <c r="E26">
+        <v>175</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="H26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27">
+        <v>26000</v>
+      </c>
+      <c r="C27">
+        <v>32941.57952708909</v>
+      </c>
+      <c r="D27">
+        <v>6941.579527089089</v>
+      </c>
+      <c r="E27">
+        <v>105</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28">
+        <v>32000</v>
+      </c>
+      <c r="C28">
+        <v>38452.45744015665</v>
+      </c>
+      <c r="D28">
+        <v>6452.45744015665</v>
+      </c>
+      <c r="E28">
+        <v>110</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="H28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29">
+        <v>26500</v>
+      </c>
+      <c r="C29">
+        <v>32935.11952385221</v>
+      </c>
+      <c r="D29">
+        <v>6435.119523852212</v>
+      </c>
+      <c r="E29">
+        <v>100</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="H29" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>3</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30">
         <v>35000</v>
       </c>
-      <c r="C22">
-        <v>35157.15338716295</v>
-      </c>
-      <c r="D22">
-        <v>157.1533871629508</v>
-      </c>
-      <c r="E22">
+      <c r="C30">
+        <v>41208.810719983</v>
+      </c>
+      <c r="D30">
+        <v>6208.810719983005</v>
+      </c>
+      <c r="E30">
         <v>100</v>
       </c>
-      <c r="F22">
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+      <c r="H30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31">
+        <v>26500</v>
+      </c>
+      <c r="C31">
+        <v>32407.25875517487</v>
+      </c>
+      <c r="D31">
+        <v>5907.258755174869</v>
+      </c>
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
         <v>3</v>
       </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="H31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31">
+        <v>3</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32">
+        <v>32000</v>
+      </c>
+      <c r="C32">
+        <v>37861.16896304933</v>
+      </c>
+      <c r="D32">
+        <v>5861.168963049327</v>
+      </c>
+      <c r="E32">
+        <v>100</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="H32" t="s">
+        <v>26</v>
+      </c>
+      <c r="I32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33">
+        <v>30000</v>
+      </c>
+      <c r="C33">
+        <v>35842.16580633933</v>
+      </c>
+      <c r="D33">
+        <v>5842.165806339326</v>
+      </c>
+      <c r="E33">
+        <v>100</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34">
+        <v>31000</v>
+      </c>
+      <c r="C34">
+        <v>36818.65480184829</v>
+      </c>
+      <c r="D34">
+        <v>5818.654801848294</v>
+      </c>
+      <c r="E34">
+        <v>105</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
         <v>27</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I34" t="s">
         <v>32</v>
       </c>
-      <c r="J22">
-        <v>2</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>53</v>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35">
+        <v>26000</v>
+      </c>
+      <c r="C35">
+        <v>31385.26281726712</v>
+      </c>
+      <c r="D35">
+        <v>5385.262817267117</v>
+      </c>
+      <c r="E35">
+        <v>80</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="H35" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36">
+        <v>25000</v>
+      </c>
+      <c r="C36">
+        <v>30330.84606220433</v>
+      </c>
+      <c r="D36">
+        <v>5330.846062204331</v>
+      </c>
+      <c r="E36">
+        <v>70</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="H36" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37">
+        <v>27000</v>
+      </c>
+      <c r="C37">
+        <v>32324.49444767221</v>
+      </c>
+      <c r="D37">
+        <v>5324.494447672212</v>
+      </c>
+      <c r="E37">
+        <v>100</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="H37" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38">
+        <v>28500</v>
+      </c>
+      <c r="C38">
+        <v>33783.56048568049</v>
+      </c>
+      <c r="D38">
+        <v>5283.560485680493</v>
+      </c>
+      <c r="E38">
+        <v>150</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="H38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39">
+        <v>26750</v>
+      </c>
+      <c r="C39">
+        <v>32026.28129083755</v>
+      </c>
+      <c r="D39">
+        <v>5276.281290837545</v>
+      </c>
+      <c r="E39">
+        <v>90</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="H39" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" t="s">
+        <v>26</v>
+      </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40">
+        <v>22000</v>
+      </c>
+      <c r="C40">
+        <v>27269.24294595521</v>
+      </c>
+      <c r="D40">
+        <v>5269.242945955208</v>
+      </c>
+      <c r="E40">
+        <v>79</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="H40" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40" t="s">
+        <v>26</v>
+      </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41">
+        <v>27500</v>
+      </c>
+      <c r="C41">
+        <v>32590.47742810858</v>
+      </c>
+      <c r="D41">
+        <v>5090.477428108581</v>
+      </c>
+      <c r="E41">
+        <v>90</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="H41" t="s">
+        <v>28</v>
+      </c>
+      <c r="I41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41">
+        <v>4</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42">
+        <v>26750</v>
+      </c>
+      <c r="C42">
+        <v>31837.47539314579</v>
+      </c>
+      <c r="D42">
+        <v>5087.475393145793</v>
+      </c>
+      <c r="E42">
+        <v>85</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" t="s">
+        <v>26</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43">
+        <v>30000</v>
+      </c>
+      <c r="C43">
+        <v>35036.469463298</v>
+      </c>
+      <c r="D43">
+        <v>5036.469463298003</v>
+      </c>
+      <c r="E43">
+        <v>90</v>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <v>7</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44">
+        <v>30000</v>
+      </c>
+      <c r="C44">
+        <v>35036.469463298</v>
+      </c>
+      <c r="D44">
+        <v>5036.469463298003</v>
+      </c>
+      <c r="E44">
+        <v>90</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="H44" t="s">
+        <v>27</v>
+      </c>
+      <c r="I44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44">
+        <v>7</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45">
+        <v>27500</v>
+      </c>
+      <c r="C45">
+        <v>32193.69040249339</v>
+      </c>
+      <c r="D45">
+        <v>4693.69040249339</v>
+      </c>
+      <c r="E45">
+        <v>90</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="H45" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" t="s">
+        <v>26</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45">
+        <v>4</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46">
+        <v>34000</v>
+      </c>
+      <c r="C46">
+        <v>38647.55417170127</v>
+      </c>
+      <c r="D46">
+        <v>4647.554171701275</v>
+      </c>
+      <c r="E46">
+        <v>120</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="H46" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" t="s">
+        <v>26</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47">
+        <v>28000</v>
+      </c>
+      <c r="C47">
+        <v>32400.75020313868</v>
+      </c>
+      <c r="D47">
+        <v>4400.750203138679</v>
+      </c>
+      <c r="E47">
+        <v>105</v>
+      </c>
+      <c r="F47">
+        <v>3</v>
+      </c>
+      <c r="H47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47" t="s">
+        <v>26</v>
+      </c>
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48">
+        <v>27500</v>
+      </c>
+      <c r="C48">
+        <v>31550.77491455053</v>
+      </c>
+      <c r="D48">
+        <v>4050.77491455053</v>
+      </c>
+      <c r="E48">
+        <v>85</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="H48" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" t="s">
+        <v>26</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49">
+        <v>23000</v>
+      </c>
+      <c r="C49">
+        <v>26849.55026690996</v>
+      </c>
+      <c r="D49">
+        <v>3849.550266909959</v>
+      </c>
+      <c r="E49">
+        <v>55</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="H49" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" t="s">
+        <v>26</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50">
+        <v>23000</v>
+      </c>
+      <c r="C50">
+        <v>26672.45724575309</v>
+      </c>
+      <c r="D50">
+        <v>3672.457245753092</v>
+      </c>
+      <c r="E50">
+        <v>55</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="H50" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51">
+        <v>35000</v>
+      </c>
+      <c r="C51">
+        <v>38647.55417170127</v>
+      </c>
+      <c r="D51">
+        <v>3647.554171701275</v>
+      </c>
+      <c r="E51">
+        <v>120</v>
+      </c>
+      <c r="F51">
+        <v>4</v>
+      </c>
+      <c r="H51" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52">
+        <v>28500</v>
+      </c>
+      <c r="C52">
+        <v>32145.30043976404</v>
+      </c>
+      <c r="D52">
+        <v>3645.300439764036</v>
+      </c>
+      <c r="E52">
+        <v>70</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="H52" t="s">
+        <v>28</v>
+      </c>
+      <c r="I52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52">
+        <v>5</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53">
+        <v>35000</v>
+      </c>
+      <c r="C53">
+        <v>38581.63391397151</v>
+      </c>
+      <c r="D53">
+        <v>3581.633913971506</v>
+      </c>
+      <c r="E53">
+        <v>140</v>
+      </c>
+      <c r="F53">
+        <v>4</v>
+      </c>
+      <c r="H53" t="s">
+        <v>26</v>
+      </c>
+      <c r="I53" t="s">
+        <v>26</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54">
+        <v>28000</v>
+      </c>
+      <c r="C54">
+        <v>31550.77491455053</v>
+      </c>
+      <c r="D54">
+        <v>3550.77491455053</v>
+      </c>
+      <c r="E54">
+        <v>85</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="H54" t="s">
+        <v>26</v>
+      </c>
+      <c r="I54" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55">
+        <v>29000</v>
+      </c>
+      <c r="C55">
+        <v>32367.90427341807</v>
+      </c>
+      <c r="D55">
+        <v>3367.904273418073</v>
+      </c>
+      <c r="E55">
+        <v>85</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="H55" t="s">
+        <v>28</v>
+      </c>
+      <c r="I55" t="s">
+        <v>26</v>
+      </c>
+      <c r="J55">
+        <v>2</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56">
+        <v>29000</v>
+      </c>
+      <c r="C56">
+        <v>32257.86514998718</v>
+      </c>
+      <c r="D56">
+        <v>3257.865149987181</v>
+      </c>
+      <c r="E56">
+        <v>75</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="H56" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" t="s">
+        <v>26</v>
+      </c>
+      <c r="J56">
+        <v>2</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57">
+        <v>33000</v>
+      </c>
+      <c r="C57">
+        <v>36171.31041900884</v>
+      </c>
+      <c r="D57">
+        <v>3171.310419008842</v>
+      </c>
+      <c r="E57">
+        <v>90</v>
+      </c>
+      <c r="F57">
+        <v>3</v>
+      </c>
+      <c r="H57" t="s">
+        <v>27</v>
+      </c>
+      <c r="I57" t="s">
+        <v>26</v>
+      </c>
+      <c r="J57">
+        <v>2</v>
+      </c>
+      <c r="K57">
+        <v>13</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58">
+        <v>27000</v>
+      </c>
+      <c r="C58">
+        <v>30152.03533589745</v>
+      </c>
+      <c r="D58">
+        <v>3152.035335897453</v>
+      </c>
+      <c r="E58">
+        <v>65</v>
+      </c>
+      <c r="F58">
+        <v>2</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58" t="s">
+        <v>33</v>
+      </c>
+      <c r="J58">
+        <v>2</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59">
+        <v>30000</v>
+      </c>
+      <c r="C59">
+        <v>33142.56730838261</v>
+      </c>
+      <c r="D59">
+        <v>3142.567308382611</v>
+      </c>
+      <c r="E59">
+        <v>105</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
+        <v>28</v>
+      </c>
+      <c r="I59" t="s">
+        <v>29</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60">
+        <v>28000</v>
+      </c>
+      <c r="C60">
+        <v>31093.31713032391</v>
+      </c>
+      <c r="D60">
+        <v>3093.317130323914</v>
+      </c>
+      <c r="E60">
+        <v>65</v>
+      </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" t="s">
+        <v>26</v>
+      </c>
+      <c r="J60">
+        <v>2</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61">
+        <v>29000</v>
+      </c>
+      <c r="C61">
+        <v>32081.34963182178</v>
+      </c>
+      <c r="D61">
+        <v>3081.349631821784</v>
+      </c>
+      <c r="E61">
+        <v>85</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="H61" t="s">
+        <v>26</v>
+      </c>
+      <c r="I61" t="s">
+        <v>26</v>
+      </c>
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62">
+        <v>33000</v>
+      </c>
+      <c r="C62">
+        <v>35997.49615615552</v>
+      </c>
+      <c r="D62">
+        <v>2997.496156155525</v>
+      </c>
+      <c r="E62">
+        <v>130</v>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" t="s">
+        <v>24</v>
+      </c>
+      <c r="B63">
+        <v>30000</v>
+      </c>
+      <c r="C63">
+        <v>32792.76824204133</v>
+      </c>
+      <c r="D63">
+        <v>2792.768242041333</v>
+      </c>
+      <c r="E63">
+        <v>110</v>
+      </c>
+      <c r="F63">
+        <v>3</v>
+      </c>
+      <c r="H63" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" t="s">
+        <v>26</v>
+      </c>
+      <c r="J63">
+        <v>2</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64">
+        <v>27000</v>
+      </c>
+      <c r="C64">
+        <v>29771.30072144041</v>
+      </c>
+      <c r="D64">
+        <v>2771.300721440406</v>
+      </c>
+      <c r="E64">
+        <v>75</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+      <c r="H64" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" t="s">
+        <v>26</v>
+      </c>
+      <c r="J64">
+        <v>2</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B65">
+        <v>29500</v>
+      </c>
+      <c r="C65">
+        <v>32172.52092228123</v>
+      </c>
+      <c r="D65">
+        <v>2672.520922281226</v>
+      </c>
+      <c r="E65">
+        <v>90</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="H65" t="s">
+        <v>26</v>
+      </c>
+      <c r="I65" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" t="s">
+        <v>23</v>
+      </c>
+      <c r="B66">
+        <v>30000</v>
+      </c>
+      <c r="C66">
+        <v>32665.26234137686</v>
+      </c>
+      <c r="D66">
+        <v>2665.262341376863</v>
+      </c>
+      <c r="E66">
+        <v>118</v>
+      </c>
+      <c r="F66">
+        <v>3</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>26</v>
+      </c>
+      <c r="I66" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66">
+        <v>2</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67">
+        <v>28500</v>
+      </c>
+      <c r="C67">
+        <v>31056.83884585951</v>
+      </c>
+      <c r="D67">
+        <v>2556.838845859515</v>
+      </c>
+      <c r="E67">
+        <v>70</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+      <c r="H67" t="s">
+        <v>26</v>
+      </c>
+      <c r="I67" t="s">
+        <v>26</v>
+      </c>
+      <c r="J67">
+        <v>2</v>
+      </c>
+      <c r="K67">
+        <v>5</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68">
+        <v>25500</v>
+      </c>
+      <c r="C68">
+        <v>28049.58014031099</v>
+      </c>
+      <c r="D68">
+        <v>2549.580140310987</v>
+      </c>
+      <c r="E68">
+        <v>80</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="H68" t="s">
+        <v>28</v>
+      </c>
+      <c r="I68" t="s">
+        <v>26</v>
+      </c>
+      <c r="J68">
+        <v>2</v>
+      </c>
+      <c r="K68">
+        <v>2</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69">
+        <v>24500</v>
+      </c>
+      <c r="C69">
+        <v>27018.3947142425</v>
+      </c>
+      <c r="D69">
+        <v>2518.394714242499</v>
+      </c>
+      <c r="E69">
+        <v>55</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="H69" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" t="s">
+        <v>26</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70">
+        <v>25000</v>
+      </c>
+      <c r="C70">
+        <v>27464.43354741415</v>
+      </c>
+      <c r="D70">
+        <v>2464.433547414152</v>
+      </c>
+      <c r="E70">
+        <v>75</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>28</v>
+      </c>
+      <c r="I70" t="s">
+        <v>30</v>
+      </c>
+      <c r="J70">
+        <v>2</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71">
+        <v>27000</v>
+      </c>
+      <c r="C71">
+        <v>29217.99534220124</v>
+      </c>
+      <c r="D71">
+        <v>2217.99534220124</v>
+      </c>
+      <c r="E71">
+        <v>50</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="H71" t="s">
+        <v>27</v>
+      </c>
+      <c r="I71" t="s">
+        <v>26</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72">
+        <v>30000</v>
+      </c>
+      <c r="C72">
+        <v>32216.2068648404</v>
+      </c>
+      <c r="D72">
+        <v>2216.206864840402</v>
+      </c>
+      <c r="E72">
+        <v>95</v>
+      </c>
+      <c r="F72">
+        <v>3</v>
+      </c>
+      <c r="H72" t="s">
+        <v>26</v>
+      </c>
+      <c r="I72" t="s">
+        <v>26</v>
+      </c>
+      <c r="J72">
+        <v>2</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73">
+        <v>24750</v>
+      </c>
+      <c r="C73">
+        <v>26954.80643040621</v>
+      </c>
+      <c r="D73">
+        <v>2204.806430406214</v>
+      </c>
+      <c r="E73">
+        <v>50</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>26</v>
+      </c>
+      <c r="I73" t="s">
+        <v>26</v>
+      </c>
+      <c r="J73">
+        <v>2</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74">
+        <v>25000</v>
+      </c>
+      <c r="C74">
+        <v>27178.20694496875</v>
+      </c>
+      <c r="D74">
+        <v>2178.206944968748</v>
+      </c>
+      <c r="E74">
+        <v>50</v>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+      <c r="H74" t="s">
+        <v>28</v>
+      </c>
+      <c r="I74" t="s">
+        <v>26</v>
+      </c>
+      <c r="J74">
+        <v>2</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75">
+        <v>30000</v>
+      </c>
+      <c r="C75">
+        <v>32172.52092228123</v>
+      </c>
+      <c r="D75">
+        <v>2172.520922281226</v>
+      </c>
+      <c r="E75">
+        <v>90</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="H75" t="s">
+        <v>26</v>
+      </c>
+      <c r="I75" t="s">
+        <v>26</v>
+      </c>
+      <c r="J75">
+        <v>2</v>
+      </c>
+      <c r="K75">
+        <v>7</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76">
+        <v>30000</v>
+      </c>
+      <c r="C76">
+        <v>32052.56667136109</v>
+      </c>
+      <c r="D76">
+        <v>2052.566671361092</v>
+      </c>
+      <c r="E76">
+        <v>100</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="H76" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76" t="s">
+        <v>26</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77">
+        <v>37000</v>
+      </c>
+      <c r="C77">
+        <v>38993.89624216763</v>
+      </c>
+      <c r="D77">
+        <v>1993.896242167626</v>
+      </c>
+      <c r="E77">
+        <v>130</v>
+      </c>
+      <c r="F77">
+        <v>4</v>
+      </c>
+      <c r="H77" t="s">
+        <v>26</v>
+      </c>
+      <c r="I77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" t="s">
+        <v>24</v>
+      </c>
+      <c r="B78">
+        <v>30000</v>
+      </c>
+      <c r="C78">
+        <v>31837.47539314579</v>
+      </c>
+      <c r="D78">
+        <v>1837.475393145793</v>
+      </c>
+      <c r="E78">
+        <v>85</v>
+      </c>
+      <c r="F78">
+        <v>3</v>
+      </c>
+      <c r="H78" t="s">
+        <v>26</v>
+      </c>
+      <c r="I78" t="s">
+        <v>26</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79">
+        <v>25500</v>
+      </c>
+      <c r="C79">
+        <v>27329.06489747793</v>
+      </c>
+      <c r="D79">
+        <v>1829.064897477932</v>
+      </c>
+      <c r="E79">
+        <v>80</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="H79" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79" t="s">
+        <v>26</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" t="s">
+        <v>23</v>
+      </c>
+      <c r="B80">
+        <v>25000</v>
+      </c>
+      <c r="C80">
+        <v>26786.35936155432</v>
+      </c>
+      <c r="D80">
+        <v>1786.359361554321</v>
+      </c>
+      <c r="E80">
+        <v>50</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80" t="s">
+        <v>28</v>
+      </c>
+      <c r="I80" t="s">
+        <v>26</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81">
+        <v>30000</v>
+      </c>
+      <c r="C81">
+        <v>31717.15984997154</v>
+      </c>
+      <c r="D81">
+        <v>1717.159849971536</v>
+      </c>
+      <c r="E81">
+        <v>90</v>
+      </c>
+      <c r="F81">
+        <v>3</v>
+      </c>
+      <c r="H81" t="s">
+        <v>26</v>
+      </c>
+      <c r="I81" t="s">
+        <v>26</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81">
+        <v>7</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82">
+        <v>25500</v>
+      </c>
+      <c r="C82">
+        <v>27133.23188619613</v>
+      </c>
+      <c r="D82">
+        <v>1633.231886196132</v>
+      </c>
+      <c r="E82">
+        <v>64</v>
+      </c>
+      <c r="F82">
+        <v>2</v>
+      </c>
+      <c r="H82" t="s">
+        <v>26</v>
+      </c>
+      <c r="I82" t="s">
+        <v>26</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" t="s">
+        <v>24</v>
+      </c>
+      <c r="B83">
+        <v>30000</v>
+      </c>
+      <c r="C83">
+        <v>31550.77491455053</v>
+      </c>
+      <c r="D83">
+        <v>1550.77491455053</v>
+      </c>
+      <c r="E83">
+        <v>85</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="H83" t="s">
+        <v>26</v>
+      </c>
+      <c r="I83" t="s">
+        <v>26</v>
+      </c>
+      <c r="J83">
+        <v>2</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84">
+        <v>30000</v>
+      </c>
+      <c r="C84">
+        <v>31550.77491455053</v>
+      </c>
+      <c r="D84">
+        <v>1550.77491455053</v>
+      </c>
+      <c r="E84">
+        <v>85</v>
+      </c>
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="H84" t="s">
+        <v>26</v>
+      </c>
+      <c r="I84" t="s">
+        <v>26</v>
+      </c>
+      <c r="J84">
+        <v>2</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" t="s">
+        <v>24</v>
+      </c>
+      <c r="B85">
+        <v>31000</v>
+      </c>
+      <c r="C85">
+        <v>32419.5534882641</v>
+      </c>
+      <c r="D85">
+        <v>1419.5534882641</v>
+      </c>
+      <c r="E85">
+        <v>100</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="H85" t="s">
+        <v>26</v>
+      </c>
+      <c r="I85" t="s">
+        <v>26</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" t="s">
+        <v>24</v>
+      </c>
+      <c r="B86">
+        <v>30500</v>
+      </c>
+      <c r="C86">
+        <v>31896.22167067787</v>
+      </c>
+      <c r="D86">
+        <v>1396.221670677867</v>
+      </c>
+      <c r="E86">
+        <v>85</v>
+      </c>
+      <c r="F86">
+        <v>3</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86" t="s">
+        <v>28</v>
+      </c>
+      <c r="I86" t="s">
+        <v>30</v>
+      </c>
+      <c r="J86">
+        <v>2</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" t="s">
+        <v>24</v>
+      </c>
+      <c r="B87">
+        <v>25000</v>
+      </c>
+      <c r="C87">
+        <v>26329.33531133905</v>
+      </c>
+      <c r="D87">
+        <v>1329.335311339055</v>
+      </c>
+      <c r="E87">
+        <v>56</v>
+      </c>
+      <c r="F87">
+        <v>2</v>
+      </c>
+      <c r="H87" t="s">
+        <v>26</v>
+      </c>
+      <c r="I87" t="s">
+        <v>26</v>
+      </c>
+      <c r="J87">
+        <v>2</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88">
+        <v>31000</v>
+      </c>
+      <c r="C88">
+        <v>32248.41816151449</v>
+      </c>
+      <c r="D88">
+        <v>1248.418161514488</v>
+      </c>
+      <c r="E88">
+        <v>95</v>
+      </c>
+      <c r="F88">
+        <v>3</v>
+      </c>
+      <c r="H88" t="s">
+        <v>26</v>
+      </c>
+      <c r="I88" t="s">
+        <v>26</v>
+      </c>
+      <c r="J88">
+        <v>2</v>
+      </c>
+      <c r="K88">
+        <v>9</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" t="s">
+        <v>24</v>
+      </c>
+      <c r="B89">
+        <v>37000</v>
+      </c>
+      <c r="C89">
+        <v>38040.01398848696</v>
+      </c>
+      <c r="D89">
+        <v>1040.013988486964</v>
+      </c>
+      <c r="E89">
+        <v>110</v>
+      </c>
+      <c r="F89">
+        <v>4</v>
+      </c>
+      <c r="H89" t="s">
+        <v>26</v>
+      </c>
+      <c r="I89" t="s">
+        <v>26</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90">
+        <v>31000</v>
+      </c>
+      <c r="C90">
+        <v>32033.12852720214</v>
+      </c>
+      <c r="D90">
+        <v>1033.128527202138</v>
+      </c>
+      <c r="E90">
+        <v>65</v>
+      </c>
+      <c r="F90">
+        <v>3</v>
+      </c>
+      <c r="H90" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" t="s">
+        <v>26</v>
+      </c>
+      <c r="J90">
+        <v>2</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91">
+        <v>32000</v>
+      </c>
+      <c r="C91">
+        <v>32947.18052227271</v>
+      </c>
+      <c r="D91">
+        <v>947.1805222727126</v>
+      </c>
+      <c r="E91">
+        <v>100</v>
+      </c>
+      <c r="F91">
+        <v>3</v>
+      </c>
+      <c r="H91" t="s">
+        <v>28</v>
+      </c>
+      <c r="I91" t="s">
+        <v>26</v>
+      </c>
+      <c r="J91">
+        <v>2</v>
+      </c>
+      <c r="K91">
+        <v>11</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B92">
+        <v>31000</v>
+      </c>
+      <c r="C92">
+        <v>31911.97478532425</v>
+      </c>
+      <c r="D92">
+        <v>911.9747853242479</v>
+      </c>
+      <c r="E92">
+        <v>70</v>
+      </c>
+      <c r="F92">
+        <v>3</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92" t="s">
+        <v>28</v>
+      </c>
+      <c r="I92" t="s">
+        <v>26</v>
+      </c>
+      <c r="J92">
+        <v>2</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" t="s">
+        <v>23</v>
+      </c>
+      <c r="B93">
+        <v>31000</v>
+      </c>
+      <c r="C93">
+        <v>31884.42222649534</v>
+      </c>
+      <c r="D93">
+        <v>884.4222264953351</v>
+      </c>
+      <c r="E93">
+        <v>95</v>
+      </c>
+      <c r="F93">
+        <v>3</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93" t="s">
+        <v>26</v>
+      </c>
+      <c r="I93" t="s">
+        <v>26</v>
+      </c>
+      <c r="J93">
+        <v>2</v>
+      </c>
+      <c r="K93">
+        <v>9</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" t="s">
+        <v>23</v>
+      </c>
+      <c r="B94">
+        <v>27000</v>
+      </c>
+      <c r="C94">
+        <v>27815.09979623036</v>
+      </c>
+      <c r="D94">
+        <v>815.0997962303554</v>
+      </c>
+      <c r="E94">
+        <v>115</v>
+      </c>
+      <c r="F94">
+        <v>2</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94" t="s">
+        <v>26</v>
+      </c>
+      <c r="I94" t="s">
+        <v>26</v>
+      </c>
+      <c r="J94">
+        <v>2</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95">
+        <v>30500</v>
+      </c>
+      <c r="C95">
+        <v>31227.35181140835</v>
+      </c>
+      <c r="D95">
+        <v>727.3518114083527</v>
+      </c>
+      <c r="E95">
+        <v>80</v>
+      </c>
+      <c r="F95">
+        <v>3</v>
+      </c>
+      <c r="H95" t="s">
+        <v>28</v>
+      </c>
+      <c r="I95" t="s">
+        <v>26</v>
+      </c>
+      <c r="J95">
+        <v>2</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" t="s">
+        <v>23</v>
+      </c>
+      <c r="B96">
+        <v>30500</v>
+      </c>
+      <c r="C96">
+        <v>31212.02748827276</v>
+      </c>
+      <c r="D96">
+        <v>712.0274882727608</v>
+      </c>
+      <c r="E96">
+        <v>90</v>
+      </c>
+      <c r="F96">
+        <v>3</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96" t="s">
+        <v>26</v>
+      </c>
+      <c r="I96" t="s">
+        <v>26</v>
+      </c>
+      <c r="J96">
+        <v>2</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" t="s">
+        <v>24</v>
+      </c>
+      <c r="B97">
+        <v>31000</v>
+      </c>
+      <c r="C97">
+        <v>31700.46839765928</v>
+      </c>
+      <c r="D97">
+        <v>700.4683976592751</v>
+      </c>
+      <c r="E97">
+        <v>100</v>
+      </c>
+      <c r="F97">
+        <v>3</v>
+      </c>
+      <c r="H97" t="s">
+        <v>26</v>
+      </c>
+      <c r="I97" t="s">
+        <v>26</v>
+      </c>
+      <c r="J97">
+        <v>2</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98">
+        <v>26000</v>
+      </c>
+      <c r="C98">
+        <v>26696.78134335014</v>
+      </c>
+      <c r="D98">
+        <v>696.7813433501397</v>
+      </c>
+      <c r="E98">
+        <v>65</v>
+      </c>
+      <c r="F98">
+        <v>2</v>
+      </c>
+      <c r="H98" t="s">
+        <v>26</v>
+      </c>
+      <c r="I98" t="s">
+        <v>26</v>
+      </c>
+      <c r="J98">
+        <v>2</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" t="s">
+        <v>24</v>
+      </c>
+      <c r="B99">
+        <v>30750</v>
+      </c>
+      <c r="C99">
+        <v>31212.02748827276</v>
+      </c>
+      <c r="D99">
+        <v>462.0274882727608</v>
+      </c>
+      <c r="E99">
+        <v>90</v>
+      </c>
+      <c r="F99">
+        <v>3</v>
+      </c>
+      <c r="H99" t="s">
+        <v>26</v>
+      </c>
+      <c r="I99" t="s">
+        <v>26</v>
+      </c>
+      <c r="J99">
+        <v>2</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100">
+        <v>32000</v>
+      </c>
+      <c r="C100">
+        <v>32407.25875517487</v>
+      </c>
+      <c r="D100">
+        <v>407.2587551748693</v>
+      </c>
+      <c r="E100">
+        <v>100</v>
+      </c>
+      <c r="F100">
+        <v>3</v>
+      </c>
+      <c r="H100" t="s">
+        <v>26</v>
+      </c>
+      <c r="I100" t="s">
+        <v>26</v>
+      </c>
+      <c r="J100">
+        <v>2</v>
+      </c>
+      <c r="K100">
+        <v>11</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101">
+        <v>29500</v>
+      </c>
+      <c r="C101">
+        <v>29882.5545302305</v>
+      </c>
+      <c r="D101">
+        <v>382.5545302304963</v>
+      </c>
+      <c r="E101">
+        <v>90</v>
+      </c>
+      <c r="F101">
+        <v>2</v>
+      </c>
+      <c r="H101" t="s">
+        <v>27</v>
+      </c>
+      <c r="I101" t="s">
+        <v>26</v>
+      </c>
+      <c r="J101">
+        <v>2</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" t="s">
+        <v>24</v>
+      </c>
+      <c r="B102">
+        <v>26500</v>
+      </c>
+      <c r="C102">
+        <v>26878.36950602573</v>
+      </c>
+      <c r="D102">
+        <v>378.3695060257342</v>
+      </c>
+      <c r="E102">
+        <v>66</v>
+      </c>
+      <c r="F102">
+        <v>2</v>
+      </c>
+      <c r="H102" t="s">
+        <v>26</v>
+      </c>
+      <c r="I102" t="s">
+        <v>26</v>
+      </c>
+      <c r="J102">
+        <v>2</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103">
+        <v>30000</v>
+      </c>
+      <c r="C103">
+        <v>30351.7211319884</v>
+      </c>
+      <c r="D103">
+        <v>351.7211319883972</v>
+      </c>
+      <c r="E103">
+        <v>72</v>
+      </c>
+      <c r="F103">
+        <v>3</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103" t="s">
+        <v>26</v>
+      </c>
+      <c r="I103" t="s">
+        <v>26</v>
+      </c>
+      <c r="J103">
+        <v>2</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" t="s">
+        <v>24</v>
+      </c>
+      <c r="B104">
+        <v>26500</v>
+      </c>
+      <c r="C104">
+        <v>26840.81303293741</v>
+      </c>
+      <c r="D104">
+        <v>340.8130329374108</v>
+      </c>
+      <c r="E104">
+        <v>64</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="H104" t="s">
+        <v>26</v>
+      </c>
+      <c r="I104" t="s">
+        <v>26</v>
+      </c>
+      <c r="J104">
+        <v>2</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105">
+        <v>32000</v>
+      </c>
+      <c r="C105">
+        <v>32283.84619302865</v>
+      </c>
+      <c r="D105">
+        <v>283.8461930286503</v>
+      </c>
+      <c r="E105">
+        <v>94</v>
+      </c>
+      <c r="F105">
+        <v>3</v>
+      </c>
+      <c r="H105" t="s">
+        <v>26</v>
+      </c>
+      <c r="I105" t="s">
+        <v>26</v>
+      </c>
+      <c r="J105">
+        <v>2</v>
+      </c>
+      <c r="K105">
+        <v>10</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106">
+        <v>29500</v>
+      </c>
+      <c r="C106">
+        <v>29771.30072144041</v>
+      </c>
+      <c r="D106">
+        <v>271.3007214404061</v>
+      </c>
+      <c r="E106">
+        <v>75</v>
+      </c>
+      <c r="F106">
+        <v>2</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106" t="s">
+        <v>27</v>
+      </c>
+      <c r="I106" t="s">
+        <v>26</v>
+      </c>
+      <c r="J106">
+        <v>2</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" t="s">
+        <v>24</v>
+      </c>
+      <c r="B107">
+        <v>27000</v>
+      </c>
+      <c r="C107">
+        <v>27146.02166349673</v>
+      </c>
+      <c r="D107">
+        <v>146.0216634967328</v>
+      </c>
+      <c r="E107">
+        <v>65</v>
+      </c>
+      <c r="F107">
+        <v>2</v>
+      </c>
+      <c r="H107" t="s">
+        <v>26</v>
+      </c>
+      <c r="I107" t="s">
+        <v>26</v>
+      </c>
+      <c r="J107">
+        <v>2</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" t="s">
+        <v>24</v>
+      </c>
+      <c r="B108">
+        <v>27000</v>
+      </c>
+      <c r="C108">
+        <v>27133.23188619613</v>
+      </c>
+      <c r="D108">
+        <v>133.2318861961321</v>
+      </c>
+      <c r="E108">
+        <v>64</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
+      </c>
+      <c r="H108" t="s">
+        <v>26</v>
+      </c>
+      <c r="I108" t="s">
+        <v>26</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109">
+        <v>40500</v>
+      </c>
+      <c r="C109">
+        <v>40566.2242695702</v>
+      </c>
+      <c r="D109">
+        <v>66.2242695702007</v>
+      </c>
+      <c r="E109">
+        <v>147</v>
+      </c>
+      <c r="F109">
+        <v>4</v>
+      </c>
+      <c r="H109" t="s">
+        <v>28</v>
+      </c>
+      <c r="I109" t="s">
+        <v>26</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" t="s">
+        <v>25</v>
+      </c>
+      <c r="B110">
+        <v>32000</v>
+      </c>
+      <c r="C110">
+        <v>32046.89003967684</v>
+      </c>
+      <c r="D110">
+        <v>46.89003967683675</v>
+      </c>
+      <c r="E110">
+        <v>95</v>
+      </c>
+      <c r="F110">
+        <v>3</v>
+      </c>
+      <c r="H110" t="s">
+        <v>28</v>
+      </c>
+      <c r="I110" t="s">
+        <v>26</v>
+      </c>
+      <c r="J110">
+        <v>2</v>
+      </c>
+      <c r="K110">
+        <v>10</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1491,6 +4670,94 @@
     <hyperlink ref="L20" r:id="rId19"/>
     <hyperlink ref="L21" r:id="rId20"/>
     <hyperlink ref="L22" r:id="rId21"/>
+    <hyperlink ref="L23" r:id="rId22"/>
+    <hyperlink ref="L24" r:id="rId23"/>
+    <hyperlink ref="L25" r:id="rId24"/>
+    <hyperlink ref="L26" r:id="rId25"/>
+    <hyperlink ref="L27" r:id="rId26"/>
+    <hyperlink ref="L28" r:id="rId27"/>
+    <hyperlink ref="L29" r:id="rId28"/>
+    <hyperlink ref="L30" r:id="rId29"/>
+    <hyperlink ref="L31" r:id="rId30"/>
+    <hyperlink ref="L32" r:id="rId31"/>
+    <hyperlink ref="L33" r:id="rId32"/>
+    <hyperlink ref="L34" r:id="rId33"/>
+    <hyperlink ref="L35" r:id="rId34"/>
+    <hyperlink ref="L36" r:id="rId35"/>
+    <hyperlink ref="L37" r:id="rId36"/>
+    <hyperlink ref="L38" r:id="rId37"/>
+    <hyperlink ref="L39" r:id="rId38"/>
+    <hyperlink ref="L40" r:id="rId39"/>
+    <hyperlink ref="L41" r:id="rId40"/>
+    <hyperlink ref="L42" r:id="rId41"/>
+    <hyperlink ref="L43" r:id="rId42"/>
+    <hyperlink ref="L44" r:id="rId43"/>
+    <hyperlink ref="L45" r:id="rId44"/>
+    <hyperlink ref="L46" r:id="rId45"/>
+    <hyperlink ref="L47" r:id="rId46"/>
+    <hyperlink ref="L48" r:id="rId47"/>
+    <hyperlink ref="L49" r:id="rId48"/>
+    <hyperlink ref="L50" r:id="rId49"/>
+    <hyperlink ref="L51" r:id="rId50"/>
+    <hyperlink ref="L52" r:id="rId51"/>
+    <hyperlink ref="L53" r:id="rId52"/>
+    <hyperlink ref="L54" r:id="rId53"/>
+    <hyperlink ref="L55" r:id="rId54"/>
+    <hyperlink ref="L56" r:id="rId55"/>
+    <hyperlink ref="L57" r:id="rId56"/>
+    <hyperlink ref="L58" r:id="rId57"/>
+    <hyperlink ref="L59" r:id="rId58"/>
+    <hyperlink ref="L60" r:id="rId59"/>
+    <hyperlink ref="L61" r:id="rId60"/>
+    <hyperlink ref="L62" r:id="rId61"/>
+    <hyperlink ref="L63" r:id="rId62"/>
+    <hyperlink ref="L64" r:id="rId63"/>
+    <hyperlink ref="L65" r:id="rId64"/>
+    <hyperlink ref="L66" r:id="rId65"/>
+    <hyperlink ref="L67" r:id="rId66"/>
+    <hyperlink ref="L68" r:id="rId67"/>
+    <hyperlink ref="L69" r:id="rId68"/>
+    <hyperlink ref="L70" r:id="rId69"/>
+    <hyperlink ref="L71" r:id="rId70"/>
+    <hyperlink ref="L72" r:id="rId71"/>
+    <hyperlink ref="L73" r:id="rId72"/>
+    <hyperlink ref="L74" r:id="rId73"/>
+    <hyperlink ref="L75" r:id="rId74"/>
+    <hyperlink ref="L76" r:id="rId75"/>
+    <hyperlink ref="L77" r:id="rId76"/>
+    <hyperlink ref="L78" r:id="rId77"/>
+    <hyperlink ref="L79" r:id="rId78"/>
+    <hyperlink ref="L80" r:id="rId79"/>
+    <hyperlink ref="L81" r:id="rId80"/>
+    <hyperlink ref="L82" r:id="rId81"/>
+    <hyperlink ref="L83" r:id="rId82"/>
+    <hyperlink ref="L84" r:id="rId83"/>
+    <hyperlink ref="L85" r:id="rId84"/>
+    <hyperlink ref="L86" r:id="rId85"/>
+    <hyperlink ref="L87" r:id="rId86"/>
+    <hyperlink ref="L88" r:id="rId87"/>
+    <hyperlink ref="L89" r:id="rId88"/>
+    <hyperlink ref="L90" r:id="rId89"/>
+    <hyperlink ref="L91" r:id="rId90"/>
+    <hyperlink ref="L92" r:id="rId91"/>
+    <hyperlink ref="L93" r:id="rId92"/>
+    <hyperlink ref="L94" r:id="rId93"/>
+    <hyperlink ref="L95" r:id="rId94"/>
+    <hyperlink ref="L96" r:id="rId95"/>
+    <hyperlink ref="L97" r:id="rId96"/>
+    <hyperlink ref="L98" r:id="rId97"/>
+    <hyperlink ref="L99" r:id="rId98"/>
+    <hyperlink ref="L100" r:id="rId99"/>
+    <hyperlink ref="L101" r:id="rId100"/>
+    <hyperlink ref="L102" r:id="rId101"/>
+    <hyperlink ref="L103" r:id="rId102"/>
+    <hyperlink ref="L104" r:id="rId103"/>
+    <hyperlink ref="L105" r:id="rId104"/>
+    <hyperlink ref="L106" r:id="rId105"/>
+    <hyperlink ref="L107" r:id="rId106"/>
+    <hyperlink ref="L108" r:id="rId107"/>
+    <hyperlink ref="L109" r:id="rId108"/>
+    <hyperlink ref="L110" r:id="rId109"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1498,21 +4765,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
@@ -1523,13 +4790,13 @@
         <v>45000</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>-3.364074805487288</v>
+        <v>-3.135470464484416</v>
       </c>
       <c r="D2">
-        <v>-1.711660926707347</v>
+        <v>-5.489563003946435</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -1543,10 +4810,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>-0.3225230929550283</v>
+        <v>-0.06835280788940534</v>
       </c>
       <c r="D3">
-        <v>0.345244908685533</v>
+        <v>-0.0280684972798174</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -1560,10 +4827,10 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>0.3132645729776389</v>
+        <v>0.3406766899051717</v>
       </c>
       <c r="D4">
-        <v>0.08263109819966487</v>
+        <v>-0.05534679473046713</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -1577,10 +4844,10 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>0.3251764178771316</v>
+        <v>0.3705776892924486</v>
       </c>
       <c r="D5">
-        <v>0.1136148315585506</v>
+        <v>0.1030144568519</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -1591,13 +4858,13 @@
         <v>42000</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>-2.12571828398145</v>
+        <v>-1.830651174639156</v>
       </c>
       <c r="D6">
-        <v>1.079283747587467</v>
+        <v>0.3040324050306422</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -1608,13 +4875,13 @@
         <v>35000</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>2.03140897177948</v>
+        <v>2.026578910671651</v>
       </c>
       <c r="D7">
-        <v>-0.6138698526291754</v>
+        <v>-0.3694775389281896</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
@@ -1628,10 +4895,10 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>-0.2091220366555858</v>
+        <v>0.0335087200882892</v>
       </c>
       <c r="D8">
-        <v>0.295194391254741</v>
+        <v>-0.05202870809680026</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -1642,13 +4909,13 @@
         <v>40000</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>0.7385185341005477</v>
+        <v>0.7226574198215264</v>
       </c>
       <c r="D9">
-        <v>-0.1050583421658048</v>
+        <v>-0.1451975852941529</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -1659,13 +4926,13 @@
         <v>21000</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>-1.9032727342722</v>
+        <v>-1.773701407373656</v>
       </c>
       <c r="D10">
-        <v>1.035343110825955</v>
+        <v>0.5249661497260453</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -1676,13 +4943,13 @@
         <v>25000</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>2.189428699942909</v>
+        <v>2.330580108720936</v>
       </c>
       <c r="D11">
-        <v>-0.7016096641588505</v>
+        <v>-0.50992071719642</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -1696,10 +4963,10 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>0.0416737771285259</v>
+        <v>0.1159238693482123</v>
       </c>
       <c r="D12">
-        <v>0.2387411251355304</v>
+        <v>0.1629149838943571</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -1710,13 +4977,13 @@
         <v>31000</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>0.6697361496650923</v>
+        <v>0.8229355619154219</v>
       </c>
       <c r="D13">
-        <v>-0.09269711883389624</v>
+        <v>-0.2377203419284175</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1730,10 +4997,10 @@
         <v>2</v>
       </c>
       <c r="C14">
-        <v>0.1998635166781966</v>
+        <v>0.2388151619274773</v>
       </c>
       <c r="D14">
-        <v>0.1326816156304568</v>
+        <v>-0.03138658391348427</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1744,13 +5011,13 @@
         <v>30000</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>1.792525002894861</v>
+        <v>1.974064760799004</v>
       </c>
       <c r="D15">
-        <v>-0.5264328531510788</v>
+        <v>-0.4260599793369799</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1761,13 +5028,13 @@
         <v>24500</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>3.142115968723515</v>
+        <v>3.328917015637976</v>
       </c>
       <c r="D16">
-        <v>-1.060269622329845</v>
+        <v>-0.6623200383795079</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1781,10 +5048,10 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>0.1594313963176017</v>
+        <v>0.3645586860157964</v>
       </c>
       <c r="D17">
-        <v>0.1325302096046674</v>
+        <v>-0.1298993932519946</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -1798,10 +5065,10 @@
         <v>2</v>
       </c>
       <c r="C18">
-        <v>-0.1807717725807253</v>
+        <v>0.05897410208271283</v>
       </c>
       <c r="D18">
-        <v>0.282681761897043</v>
+        <v>-0.05801876080104597</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -1815,10 +5082,10 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <v>0.1027308681678805</v>
+        <v>0.3136279220269492</v>
       </c>
       <c r="D19">
-        <v>0.1575554683200634</v>
+        <v>-0.1179192878435031</v>
       </c>
       <c r="E19" t="s">
         <v>23</v>
@@ -1832,10 +5099,10 @@
         <v>2</v>
       </c>
       <c r="C20">
-        <v>0.2161319244673229</v>
+        <v>0.4154894500046437</v>
       </c>
       <c r="D20">
-        <v>0.1075049508892715</v>
+        <v>-0.141879498660486</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
@@ -1843,19 +5110,19 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>35000</v>
+        <v>30000</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>0.7313234562436151</v>
+        <v>0.701627655219956</v>
       </c>
       <c r="D21">
-        <v>-0.05865465159945504</v>
+        <v>0.02514377169670563</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1863,67 +5130,67 @@
         <v>35000</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>-2.361302923269595</v>
+        <v>-0.06835280788940534</v>
       </c>
       <c r="D22">
-        <v>-2.17986255670652</v>
+        <v>-0.0280684972798174</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>36500</v>
+        <v>27000</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>1.092173222800719</v>
+        <v>0.6049531363767804</v>
       </c>
       <c r="D23">
-        <v>3.095757219738792</v>
+        <v>0.1303167167961834</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>35000</v>
+        <v>57500</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>-0.7549721319348695</v>
+        <v>-2.395391000762332</v>
       </c>
       <c r="D24">
-        <v>0.5793380396173526</v>
+        <v>-5.594711986552279</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>25000</v>
+        <v>31000</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>1.473477020214462</v>
+        <v>1.46634050679433</v>
       </c>
       <c r="D25">
-        <v>-0.3423902396500513</v>
+        <v>-0.2376963794347838</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1931,84 +5198,84 @@
         <v>33000</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>0.2223701342680687</v>
+        <v>-0.6779385898717737</v>
       </c>
       <c r="D26">
-        <v>0.1421483637939046</v>
+        <v>0.1842553134393616</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>35000</v>
+        <v>29500</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>-0.04207477470518716</v>
+        <v>1.720994326738567</v>
       </c>
       <c r="D27">
-        <v>0.2472292411680939</v>
+        <v>-0.2975969064772409</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>35000</v>
+        <v>31000</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>-0.1838260950794901</v>
+        <v>0.7525584192088032</v>
       </c>
       <c r="D28">
-        <v>0.3097923879565836</v>
+        <v>0.01316366628821423</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>31000</v>
+        <v>35000</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>-0.135097848945599</v>
+        <v>1.547172270170455</v>
       </c>
       <c r="D29">
-        <v>0.3057974584926537</v>
+        <v>-0.09131523326090807</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>30000</v>
+        <v>37000</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>-0.3970612455820373</v>
+        <v>0.3705776892924486</v>
       </c>
       <c r="D30">
-        <v>0.3525231942788847</v>
+        <v>0.1030144568519</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2019,166 +5286,166 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>0.2372871106852508</v>
+        <v>0.2432507793203305</v>
       </c>
       <c r="D31">
-        <v>0.1413960120979233</v>
+        <v>0.1329647203731285</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>30000</v>
+        <v>24750</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>-1.356189556136096</v>
+        <v>2.260202966014317</v>
       </c>
       <c r="D32">
-        <v>-2.498644758208535</v>
+        <v>-0.2590367089797881</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>32000</v>
+        <v>38500</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33">
-        <v>-2.20025643660846</v>
+        <v>0.3705776892924486</v>
       </c>
       <c r="D33">
-        <v>1.086562033180819</v>
+        <v>0.1030144568519</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>25500</v>
+        <v>33000</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
-        <v>-0.3297181708119608</v>
+        <v>0.3705776892924486</v>
       </c>
       <c r="D34">
-        <v>0.3916485992518828</v>
+        <v>0.1030144568519</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>1.971654121130994</v>
+        <v>-0.4697799165235313</v>
       </c>
       <c r="D35">
-        <v>-0.5617339678542388</v>
+        <v>0.3006861960920086</v>
       </c>
       <c r="E35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>52000</v>
+        <v>28000</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>-3.364074805487288</v>
+        <v>0.8798853291809214</v>
       </c>
       <c r="D36">
-        <v>-1.711660926707347</v>
+        <v>-0.01678659723301439</v>
       </c>
       <c r="E36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>-0.0390204522064224</v>
+        <v>0.7316653145687765</v>
       </c>
       <c r="D37">
-        <v>0.2201186151085533</v>
+        <v>-0.1840690194317451</v>
       </c>
       <c r="E37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>25500</v>
+        <v>35000</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>1.338920777697092</v>
+        <v>-2.175025520836595</v>
       </c>
       <c r="D38">
-        <v>-0.3262307834279112</v>
+        <v>-5.778656771455454</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>26500</v>
+        <v>36500</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>-0.1807717725807253</v>
+        <v>1.419506441482134</v>
       </c>
       <c r="D39">
-        <v>0.282681761897043</v>
+        <v>5.686646956408063</v>
       </c>
       <c r="E39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40">
-        <v>-0.1807717725807253</v>
+        <v>-0.4413256430585096</v>
       </c>
       <c r="D40">
-        <v>0.282681761897043</v>
+        <v>0.02291085914627623</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2186,84 +5453,84 @@
         <v>25000</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>1.832957123255456</v>
+        <v>1.702953453607595</v>
       </c>
       <c r="D41">
-        <v>-0.5262814471252896</v>
+        <v>-0.3990408337278691</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>40500</v>
+        <v>33000</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
       <c r="C42">
-        <v>-2.465921452879777</v>
+        <v>0.4457371175643799</v>
       </c>
       <c r="D42">
-        <v>1.229435299879843</v>
+        <v>-0.1848191377242085</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>29500</v>
+        <v>35000</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>1.265951841758244</v>
+        <v>0.1949650117991067</v>
       </c>
       <c r="D43">
-        <v>-0.27602885997133</v>
+        <v>-0.1259172835089618</v>
       </c>
       <c r="E43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>1.691205802881153</v>
+        <v>0.06763810182698844</v>
       </c>
       <c r="D44">
-        <v>-0.4637183003367997</v>
+        <v>-0.09596701998773324</v>
       </c>
       <c r="E44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>34000</v>
+        <v>31000</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>-0.0390204522064224</v>
+        <v>-0.03837672116308155</v>
       </c>
       <c r="D45">
-        <v>0.2201186151085533</v>
+        <v>-0.0005472977754265584</v>
       </c>
       <c r="E45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2274,12 +5541,2919 @@
         <v>2</v>
       </c>
       <c r="C46">
-        <v>-1.643763794708821</v>
+        <v>-0.07559238002968159</v>
       </c>
       <c r="D46">
-        <v>0.8665690485066017</v>
+        <v>-0.08954026202749918</v>
       </c>
       <c r="E46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>30500</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>0.4499627267463174</v>
+      </c>
+      <c r="D47">
+        <v>-0.1867409855023239</v>
+      </c>
+      <c r="E47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>30000</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>-1.164666756213965</v>
+      </c>
+      <c r="D48">
+        <v>-5.906533914250337</v>
+      </c>
+      <c r="E48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>32000</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>-1.837890746779432</v>
+      </c>
+      <c r="D49">
+        <v>0.2425606402829604</v>
+      </c>
+      <c r="E49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>25500</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50">
+        <v>-0.05934491314215522</v>
+      </c>
+      <c r="D50">
+        <v>-0.0669399314174095</v>
+      </c>
+      <c r="E50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>27000</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <v>1.984312146427079</v>
+      </c>
+      <c r="D51">
+        <v>-0.3954456927063854</v>
+      </c>
+      <c r="E51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>52000</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>-3.135470464484416</v>
+      </c>
+      <c r="D52">
+        <v>-5.489563003946435</v>
+      </c>
+      <c r="E52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>50000</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>-1.595443733412691</v>
+      </c>
+      <c r="D53">
+        <v>0.4830357807963253</v>
+      </c>
+      <c r="E53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>35000</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>0.5233699812589906</v>
+      </c>
+      <c r="D54">
+        <v>0.06707414062642565</v>
+      </c>
+      <c r="E54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>21000</v>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D55">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>32000</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>-1.264393767485184</v>
+      </c>
+      <c r="D56">
+        <v>0.405165095641131</v>
+      </c>
+      <c r="E56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>38000</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57">
+        <v>0.5189343638661372</v>
+      </c>
+      <c r="D57">
+        <v>-0.09727716366018715</v>
+      </c>
+      <c r="E57" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>47500</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>-2.028355227317892</v>
+      </c>
+      <c r="D58">
+        <v>0.5848666767685025</v>
+      </c>
+      <c r="E58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>53000</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>-1.595443733412691</v>
+      </c>
+      <c r="D59">
+        <v>0.4830357807963253</v>
+      </c>
+      <c r="E59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>23000</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60">
+        <v>2.132876056042199</v>
+      </c>
+      <c r="D60">
+        <v>-0.2290864454585596</v>
+      </c>
+      <c r="E60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>26000</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61">
+        <v>1.878222236097962</v>
+      </c>
+      <c r="D61">
+        <v>-0.1691859184161024</v>
+      </c>
+      <c r="E61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>31500</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>2.077509674660498</v>
+      </c>
+      <c r="D62">
+        <v>-0.381457644336681</v>
+      </c>
+      <c r="E62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>30000</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63">
+        <v>1.776360708120267</v>
+      </c>
+      <c r="D63">
+        <v>-0.1452257075991196</v>
+      </c>
+      <c r="E63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>41500</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>0.3705776892924486</v>
+      </c>
+      <c r="D64">
+        <v>0.1030144568519</v>
+      </c>
+      <c r="E64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>33000</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D65">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>47000</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>-6.571567240594336</v>
+      </c>
+      <c r="D66">
+        <v>1.48867058955925</v>
+      </c>
+      <c r="E66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>30750</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D67">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>65000</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>-3.683605056955428</v>
+      </c>
+      <c r="D68">
+        <v>0.974220102544474</v>
+      </c>
+      <c r="E68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>33000</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D69">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>33000</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>-2.919643597122719</v>
+      </c>
+      <c r="D70">
+        <v>0.7945185214171024</v>
+      </c>
+      <c r="E70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>40000</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>-2.181147519284433</v>
+      </c>
+      <c r="D71">
+        <v>0.6208069929939767</v>
+      </c>
+      <c r="E71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>28000</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72">
+        <v>1.750895326125844</v>
+      </c>
+      <c r="D72">
+        <v>-0.1392356548948739</v>
+      </c>
+      <c r="E72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>32500</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D73">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>28000</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
+        <v>-2.410335957234246</v>
+      </c>
+      <c r="D74">
+        <v>0.6747174673321882</v>
+      </c>
+      <c r="E74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>44500</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>-1.51904758742942</v>
+      </c>
+      <c r="D75">
+        <v>0.4650656226835881</v>
+      </c>
+      <c r="E75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>36000</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D76">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>25500</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77">
+        <v>1.903687618092385</v>
+      </c>
+      <c r="D77">
+        <v>-0.1751759711203482</v>
+      </c>
+      <c r="E77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>50000</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78">
+        <v>-1.51904758742942</v>
+      </c>
+      <c r="D78">
+        <v>0.4650656226835881</v>
+      </c>
+      <c r="E78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>35000</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79">
+        <v>0.4979045992645669</v>
+      </c>
+      <c r="D79">
+        <v>0.07306419333067136</v>
+      </c>
+      <c r="E79" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>31000</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D80">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>27000</v>
+      </c>
+      <c r="B81">
+        <v>2</v>
+      </c>
+      <c r="C81">
+        <v>1.903687618092385</v>
+      </c>
+      <c r="D81">
+        <v>-0.1751759711203482</v>
+      </c>
+      <c r="E81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>34000</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>-1.51904758742942</v>
+      </c>
+      <c r="D82">
+        <v>0.4650656226835881</v>
+      </c>
+      <c r="E82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83">
+        <v>38250</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D83">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
+        <v>41000</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>-2.028355227317892</v>
+      </c>
+      <c r="D84">
+        <v>0.5848666767685025</v>
+      </c>
+      <c r="E84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85">
+        <v>29000</v>
+      </c>
+      <c r="B85">
+        <v>2</v>
+      </c>
+      <c r="C85">
+        <v>0.4409548319990673</v>
+      </c>
+      <c r="D85">
+        <v>-0.1478695513647318</v>
+      </c>
+      <c r="E85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86">
+        <v>25500</v>
+      </c>
+      <c r="B86">
+        <v>2</v>
+      </c>
+      <c r="C86">
+        <v>1.496241506181607</v>
+      </c>
+      <c r="D86">
+        <v>-0.0793351278524167</v>
+      </c>
+      <c r="E86" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87">
+        <v>45000</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>-1.595443733412691</v>
+      </c>
+      <c r="D87">
+        <v>0.4830357807963253</v>
+      </c>
+      <c r="E87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88">
+        <v>35000</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D88">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E88" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89">
+        <v>34500</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89">
+        <v>0.2687161613147541</v>
+      </c>
+      <c r="D89">
+        <v>0.1269746676688829</v>
+      </c>
+      <c r="E89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90">
+        <v>33000</v>
+      </c>
+      <c r="B90">
+        <v>2</v>
+      </c>
+      <c r="C90">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D90">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E90" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91">
+        <v>39000</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
+      </c>
+      <c r="C91">
+        <v>0.2941815433091777</v>
+      </c>
+      <c r="D91">
+        <v>0.1209846149646371</v>
+      </c>
+      <c r="E91" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92">
+        <v>27500</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+      <c r="C92">
+        <v>0.3705776892924486</v>
+      </c>
+      <c r="D92">
+        <v>0.1030144568519</v>
+      </c>
+      <c r="E92" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93">
+        <v>50000</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93">
+        <v>-1.595443733412691</v>
+      </c>
+      <c r="D93">
+        <v>0.4830357807963253</v>
+      </c>
+      <c r="E93" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94">
+        <v>32000</v>
+      </c>
+      <c r="B94">
+        <v>2</v>
+      </c>
+      <c r="C94">
+        <v>0.141389251342636</v>
+      </c>
+      <c r="D94">
+        <v>0.1569249311901114</v>
+      </c>
+      <c r="E94" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95">
+        <v>27000</v>
+      </c>
+      <c r="B95">
+        <v>2</v>
+      </c>
+      <c r="C95">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D95">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E95" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96">
+        <v>32500</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <v>-0.9887101829393763</v>
+      </c>
+      <c r="D96">
+        <v>0.1749232116078153</v>
+      </c>
+      <c r="E96" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97">
+        <v>38500</v>
+      </c>
+      <c r="B97">
+        <v>2</v>
+      </c>
+      <c r="C97">
+        <v>0.141389251342636</v>
+      </c>
+      <c r="D97">
+        <v>0.1569249311901114</v>
+      </c>
+      <c r="E97" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98">
+        <v>45000</v>
+      </c>
+      <c r="B98">
+        <v>2</v>
+      </c>
+      <c r="C98">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D98">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E98" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99">
+        <v>25000</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99">
+        <v>2.107410674047776</v>
+      </c>
+      <c r="D99">
+        <v>-0.2230963927543139</v>
+      </c>
+      <c r="E99" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100">
+        <v>31000</v>
+      </c>
+      <c r="B100">
+        <v>2</v>
+      </c>
+      <c r="C100">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D100">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E100" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101">
+        <v>45000</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>-2.212631904555509</v>
+      </c>
+      <c r="D101">
+        <v>0.3938831955943279</v>
+      </c>
+      <c r="E101" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102">
+        <v>43000</v>
+      </c>
+      <c r="B102">
+        <v>2</v>
+      </c>
+      <c r="C102">
+        <v>-0.138729950596024</v>
+      </c>
+      <c r="D102">
+        <v>0.2228155109368143</v>
+      </c>
+      <c r="E102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103">
+        <v>42000</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103">
+        <v>-1.264393767485184</v>
+      </c>
+      <c r="D103">
+        <v>0.405165095641131</v>
+      </c>
+      <c r="E103" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104">
+        <v>34000</v>
+      </c>
+      <c r="B104">
+        <v>2</v>
+      </c>
+      <c r="C104">
+        <v>1.852756854103538</v>
+      </c>
+      <c r="D104">
+        <v>-0.1631958657118568</v>
+      </c>
+      <c r="E104" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105">
+        <v>31000</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+      <c r="C105">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D105">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E105" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106">
+        <v>27000</v>
+      </c>
+      <c r="B106">
+        <v>2</v>
+      </c>
+      <c r="C106">
+        <v>1.878222236097962</v>
+      </c>
+      <c r="D106">
+        <v>-0.1691859184161024</v>
+      </c>
+      <c r="E106" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107">
+        <v>52000</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107">
+        <v>-1.977424463329045</v>
+      </c>
+      <c r="D107">
+        <v>0.572886571360011</v>
+      </c>
+      <c r="E107" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108">
+        <v>31000</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108">
+        <v>-1.264393767485184</v>
+      </c>
+      <c r="D108">
+        <v>0.405165095641131</v>
+      </c>
+      <c r="E108" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109">
+        <v>28500</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109">
+        <v>-1.009739947540947</v>
+      </c>
+      <c r="D109">
+        <v>0.3452645685986738</v>
+      </c>
+      <c r="E109" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110">
+        <v>45000</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+      <c r="C110">
+        <v>-0.2660568605681423</v>
+      </c>
+      <c r="D110">
+        <v>0.2527657744580429</v>
+      </c>
+      <c r="E110" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111">
+        <v>35000</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D111">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E111" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112">
+        <v>49000</v>
+      </c>
+      <c r="B112">
+        <v>2</v>
+      </c>
+      <c r="C112">
+        <v>-0.3933837705402604</v>
+      </c>
+      <c r="D112">
+        <v>0.2827160379792715</v>
+      </c>
+      <c r="E112" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113">
+        <v>35000</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113">
+        <v>0.3705776892924486</v>
+      </c>
+      <c r="D113">
+        <v>0.1030144568519</v>
+      </c>
+      <c r="E113" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114">
+        <v>34000</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D114">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E114" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115">
+        <v>22000</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115">
+        <v>1.521706888176031</v>
+      </c>
+      <c r="D115">
+        <v>-0.08532518055666238</v>
+      </c>
+      <c r="E115" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116">
+        <v>26000</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>0.4979045992645669</v>
+      </c>
+      <c r="D116">
+        <v>0.07306419333067136</v>
+      </c>
+      <c r="E116" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117">
+        <v>30000</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>-1.468116823440572</v>
+      </c>
+      <c r="D117">
+        <v>0.4530855172750967</v>
+      </c>
+      <c r="E117" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118">
+        <v>20000</v>
+      </c>
+      <c r="B118">
+        <v>2</v>
+      </c>
+      <c r="C118">
+        <v>-0.2660568605681423</v>
+      </c>
+      <c r="D118">
+        <v>0.2527657744580429</v>
+      </c>
+      <c r="E118" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119">
+        <v>34000</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+      <c r="C119">
+        <v>0.141389251342636</v>
+      </c>
+      <c r="D119">
+        <v>0.1569249311901114</v>
+      </c>
+      <c r="E119" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120">
+        <v>28000</v>
+      </c>
+      <c r="B120">
+        <v>2</v>
+      </c>
+      <c r="C120">
+        <v>-0.138729950596024</v>
+      </c>
+      <c r="D120">
+        <v>0.2228155109368143</v>
+      </c>
+      <c r="E120" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121">
+        <v>35000</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+      <c r="C121">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D121">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122">
+        <v>33000</v>
+      </c>
+      <c r="B122">
+        <v>2</v>
+      </c>
+      <c r="C122">
+        <v>0.2941815433091777</v>
+      </c>
+      <c r="D122">
+        <v>0.1209846149646371</v>
+      </c>
+      <c r="E122" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123">
+        <v>41000</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>-0.5461760625068022</v>
+      </c>
+      <c r="D123">
+        <v>0.3186563542047458</v>
+      </c>
+      <c r="E123" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124">
+        <v>30000</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D124">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E124" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125">
+        <v>45500</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125">
+        <v>-1.595443733412691</v>
+      </c>
+      <c r="D125">
+        <v>0.4830357807963253</v>
+      </c>
+      <c r="E125" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126">
+        <v>35000</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126">
+        <v>-2.028355227317892</v>
+      </c>
+      <c r="D126">
+        <v>0.5848666767685025</v>
+      </c>
+      <c r="E126" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127">
+        <v>30000</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D127">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E127" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128">
+        <v>28500</v>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128">
+        <v>-1.284672140345088</v>
+      </c>
+      <c r="D128">
+        <v>0.4923678826278716</v>
+      </c>
+      <c r="E128" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129">
+        <v>20000</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+      <c r="C129">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D129">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130">
+        <v>23000</v>
+      </c>
+      <c r="B130">
+        <v>2</v>
+      </c>
+      <c r="C130">
+        <v>2.203253198748818</v>
+      </c>
+      <c r="D130">
+        <v>-0.4799704536751914</v>
+      </c>
+      <c r="E130" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131">
+        <v>31000</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131">
+        <v>-1.264393767485184</v>
+      </c>
+      <c r="D131">
+        <v>0.405165095641131</v>
+      </c>
+      <c r="E131" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132">
+        <v>31000</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132">
+        <v>-1.51904758742942</v>
+      </c>
+      <c r="D132">
+        <v>0.4650656226835881</v>
+      </c>
+      <c r="E132" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133">
+        <v>30000</v>
+      </c>
+      <c r="B133">
+        <v>2</v>
+      </c>
+      <c r="C133">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D133">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E133" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134">
+        <v>33000</v>
+      </c>
+      <c r="B134">
+        <v>2</v>
+      </c>
+      <c r="C134">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D134">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E134" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135">
+        <v>27000</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135">
+        <v>1.903687618092385</v>
+      </c>
+      <c r="D135">
+        <v>-0.1751759711203482</v>
+      </c>
+      <c r="E135" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136">
+        <v>27000</v>
+      </c>
+      <c r="B136">
+        <v>2</v>
+      </c>
+      <c r="C136">
+        <v>1.903687618092385</v>
+      </c>
+      <c r="D136">
+        <v>-0.1751759711203482</v>
+      </c>
+      <c r="E136" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137">
+        <v>24500</v>
+      </c>
+      <c r="B137">
+        <v>2</v>
+      </c>
+      <c r="C137">
+        <v>2.132876056042199</v>
+      </c>
+      <c r="D137">
+        <v>-0.2290864454585596</v>
+      </c>
+      <c r="E137" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138">
+        <v>40000</v>
+      </c>
+      <c r="B138">
+        <v>2</v>
+      </c>
+      <c r="C138">
+        <v>0.6252315092366851</v>
+      </c>
+      <c r="D138">
+        <v>0.04311392980944279</v>
+      </c>
+      <c r="E138" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139">
+        <v>35500</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139">
+        <v>0.6252315092366851</v>
+      </c>
+      <c r="D139">
+        <v>0.04311392980944279</v>
+      </c>
+      <c r="E139" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140">
+        <v>30000</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140">
+        <v>1.878222236097962</v>
+      </c>
+      <c r="D140">
+        <v>-0.1691859184161024</v>
+      </c>
+      <c r="E140" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141">
+        <v>29500</v>
+      </c>
+      <c r="B141">
+        <v>2</v>
+      </c>
+      <c r="C141">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D141">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E141" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142">
+        <v>38250</v>
+      </c>
+      <c r="B142">
+        <v>2</v>
+      </c>
+      <c r="C142">
+        <v>0.0860228699609354</v>
+      </c>
+      <c r="D142">
+        <v>0.004553732311990042</v>
+      </c>
+      <c r="E142" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143">
+        <v>30000</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143">
+        <v>0.3705776892924486</v>
+      </c>
+      <c r="D143">
+        <v>0.1030144568519</v>
+      </c>
+      <c r="E143" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144">
+        <v>23000</v>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="C144">
+        <v>-0.775364500456615</v>
+      </c>
+      <c r="D144">
+        <v>0.3725668285429573</v>
+      </c>
+      <c r="E144" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145">
+        <v>32000</v>
+      </c>
+      <c r="B145">
+        <v>2</v>
+      </c>
+      <c r="C145">
+        <v>0.141389251342636</v>
+      </c>
+      <c r="D145">
+        <v>0.1569249311901114</v>
+      </c>
+      <c r="E145" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146">
+        <v>25000</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+      <c r="C146">
+        <v>2.330580108720936</v>
+      </c>
+      <c r="D146">
+        <v>-0.50992071719642</v>
+      </c>
+      <c r="E146" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147">
+        <v>32000</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D147">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E147" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148">
+        <v>28750</v>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="C148">
+        <v>-2.028355227317892</v>
+      </c>
+      <c r="D148">
+        <v>0.5848666767685025</v>
+      </c>
+      <c r="E148" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149">
+        <v>48000</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149">
+        <v>-1.595443733412691</v>
+      </c>
+      <c r="D149">
+        <v>0.4830357807963253</v>
+      </c>
+      <c r="E149" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150">
+        <v>42500</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D150">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E150" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151">
+        <v>29000</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151">
+        <v>0.3705776892924486</v>
+      </c>
+      <c r="D151">
+        <v>0.1030144568519</v>
+      </c>
+      <c r="E151" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152">
+        <v>28500</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>0.7525584192088032</v>
+      </c>
+      <c r="D152">
+        <v>0.01316366628821423</v>
+      </c>
+      <c r="E152" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153">
+        <v>27500</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D153">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E153" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154">
+        <v>46000</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154">
+        <v>-1.595443733412691</v>
+      </c>
+      <c r="D154">
+        <v>0.4830357807963253</v>
+      </c>
+      <c r="E154" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155">
+        <v>30500</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155">
+        <v>0.5682817419711856</v>
+      </c>
+      <c r="D155">
+        <v>-0.1778198148859604</v>
+      </c>
+      <c r="E155" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156">
+        <v>44000</v>
+      </c>
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156">
+        <v>-0.780551509591134</v>
+      </c>
+      <c r="D156">
+        <v>0.2913540942604623</v>
+      </c>
+      <c r="E156" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157">
+        <v>45000</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+      <c r="C157">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D157">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E157" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158">
+        <v>47000</v>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158">
+        <v>-1.595443733412691</v>
+      </c>
+      <c r="D158">
+        <v>0.4830357807963253</v>
+      </c>
+      <c r="E158" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159">
+        <v>37000</v>
+      </c>
+      <c r="B159">
+        <v>1</v>
+      </c>
+      <c r="C159">
+        <v>-1.773701407373656</v>
+      </c>
+      <c r="D159">
+        <v>0.5249661497260453</v>
+      </c>
+      <c r="E159" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160">
+        <v>50000</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160">
+        <v>-1.595443733412691</v>
+      </c>
+      <c r="D160">
+        <v>0.4830357807963253</v>
+      </c>
+      <c r="E160" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161">
+        <v>30000</v>
+      </c>
+      <c r="B161">
+        <v>2</v>
+      </c>
+      <c r="C161">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D161">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E161" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162">
+        <v>30000</v>
+      </c>
+      <c r="B162">
+        <v>2</v>
+      </c>
+      <c r="C162">
+        <v>2.005549146070081</v>
+      </c>
+      <c r="D162">
+        <v>-0.199136181937331</v>
+      </c>
+      <c r="E162" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163">
+        <v>33999</v>
+      </c>
+      <c r="B163">
+        <v>1</v>
+      </c>
+      <c r="C163">
+        <v>-2.175960510149914</v>
+      </c>
+      <c r="D163">
+        <v>0.7020197272764716</v>
+      </c>
+      <c r="E163" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164">
+        <v>39000</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D164">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E164" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165">
+        <v>42000</v>
+      </c>
+      <c r="B165">
+        <v>1</v>
+      </c>
+      <c r="C165">
+        <v>-1.901028317345774</v>
+      </c>
+      <c r="D165">
+        <v>0.5549164132472738</v>
+      </c>
+      <c r="E165" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166">
+        <v>28000</v>
+      </c>
+      <c r="B166">
+        <v>2</v>
+      </c>
+      <c r="C166">
+        <v>1.903687618092385</v>
+      </c>
+      <c r="D166">
+        <v>-0.1751759711203482</v>
+      </c>
+      <c r="E166" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167">
+        <v>26750</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
+      </c>
+      <c r="C167">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D167">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E167" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168">
+        <v>35000</v>
+      </c>
+      <c r="B168">
+        <v>1</v>
+      </c>
+      <c r="C168">
+        <v>-1.51904758742942</v>
+      </c>
+      <c r="D168">
+        <v>0.4650656226835881</v>
+      </c>
+      <c r="E168" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169">
+        <v>46000</v>
+      </c>
+      <c r="B169">
+        <v>1</v>
+      </c>
+      <c r="C169">
+        <v>-1.421621676844578</v>
+      </c>
+      <c r="D169">
+        <v>0.2767541075799924</v>
+      </c>
+      <c r="E169" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170">
+        <v>24000</v>
+      </c>
+      <c r="B170">
+        <v>2</v>
+      </c>
+      <c r="C170">
+        <v>0.2432507793203305</v>
+      </c>
+      <c r="D170">
+        <v>0.1329647203731285</v>
+      </c>
+      <c r="E170" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171">
+        <v>26500</v>
+      </c>
+      <c r="B171">
+        <v>2</v>
+      </c>
+      <c r="C171">
+        <v>1.852756854103538</v>
+      </c>
+      <c r="D171">
+        <v>-0.1631958657118568</v>
+      </c>
+      <c r="E171" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172">
+        <v>42000</v>
+      </c>
+      <c r="B172">
+        <v>1</v>
+      </c>
+      <c r="C172">
+        <v>-1.264393767485184</v>
+      </c>
+      <c r="D172">
+        <v>0.405165095641131</v>
+      </c>
+      <c r="E172" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173">
+        <v>28000</v>
+      </c>
+      <c r="B173">
+        <v>2</v>
+      </c>
+      <c r="C173">
+        <v>0.3705776892924486</v>
+      </c>
+      <c r="D173">
+        <v>0.1030144568519</v>
+      </c>
+      <c r="E173" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174">
+        <v>37000</v>
+      </c>
+      <c r="B174">
+        <v>1</v>
+      </c>
+      <c r="C174">
+        <v>-1.264393767485184</v>
+      </c>
+      <c r="D174">
+        <v>0.405165095641131</v>
+      </c>
+      <c r="E174" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175">
+        <v>37000</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
+      </c>
+      <c r="C175">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D175">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E175" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176">
+        <v>42000</v>
+      </c>
+      <c r="B176">
+        <v>1</v>
+      </c>
+      <c r="C176">
+        <v>-1.51904758742942</v>
+      </c>
+      <c r="D176">
+        <v>0.4650656226835881</v>
+      </c>
+      <c r="E176" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177">
+        <v>30000</v>
+      </c>
+      <c r="B177">
+        <v>2</v>
+      </c>
+      <c r="C177">
+        <v>0.3705776892924486</v>
+      </c>
+      <c r="D177">
+        <v>0.1030144568519</v>
+      </c>
+      <c r="E177" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178">
+        <v>24000</v>
+      </c>
+      <c r="B178">
+        <v>2</v>
+      </c>
+      <c r="C178">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D178">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E178" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179">
+        <v>32000</v>
+      </c>
+      <c r="B179">
+        <v>1</v>
+      </c>
+      <c r="C179">
+        <v>-1.009739947540947</v>
+      </c>
+      <c r="D179">
+        <v>0.3452645685986738</v>
+      </c>
+      <c r="E179" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180">
+        <v>35000</v>
+      </c>
+      <c r="B180">
+        <v>1</v>
+      </c>
+      <c r="C180">
+        <v>-0.6735029724789204</v>
+      </c>
+      <c r="D180">
+        <v>0.3486066177259744</v>
+      </c>
+      <c r="E180" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181">
+        <v>26500</v>
+      </c>
+      <c r="B181">
+        <v>2</v>
+      </c>
+      <c r="C181">
+        <v>1.903687618092385</v>
+      </c>
+      <c r="D181">
+        <v>-0.1751759711203482</v>
+      </c>
+      <c r="E181" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182">
+        <v>27500</v>
+      </c>
+      <c r="B182">
+        <v>2</v>
+      </c>
+      <c r="C182">
+        <v>1.72542994413142</v>
+      </c>
+      <c r="D182">
+        <v>-0.1332456021906282</v>
+      </c>
+      <c r="E182" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183">
+        <v>26500</v>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+      <c r="C183">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D183">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E183" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184">
+        <v>44000</v>
+      </c>
+      <c r="B184">
+        <v>2</v>
+      </c>
+      <c r="C184">
+        <v>-0.01140304062390586</v>
+      </c>
+      <c r="D184">
+        <v>0.1928652474155857</v>
+      </c>
+      <c r="E184" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185">
+        <v>39000</v>
+      </c>
+      <c r="B185">
+        <v>1</v>
+      </c>
+      <c r="C185">
+        <v>-1.51904758742942</v>
+      </c>
+      <c r="D185">
+        <v>0.4650656226835881</v>
+      </c>
+      <c r="E185" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186">
+        <v>24000</v>
+      </c>
+      <c r="B186">
+        <v>2</v>
+      </c>
+      <c r="C186">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D186">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E186" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187">
+        <v>30000</v>
+      </c>
+      <c r="B187">
+        <v>2</v>
+      </c>
+      <c r="C187">
+        <v>0.3705776892924486</v>
+      </c>
+      <c r="D187">
+        <v>0.1030144568519</v>
+      </c>
+      <c r="E187" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188">
+        <v>30000</v>
+      </c>
+      <c r="B188">
+        <v>1</v>
+      </c>
+      <c r="C188">
+        <v>-2.028355227317892</v>
+      </c>
+      <c r="D188">
+        <v>0.5848666767685025</v>
+      </c>
+      <c r="E188" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189">
+        <v>19500</v>
+      </c>
+      <c r="B189">
+        <v>2</v>
+      </c>
+      <c r="C189">
+        <v>-0.2660568605681423</v>
+      </c>
+      <c r="D189">
+        <v>0.2527657744580429</v>
+      </c>
+      <c r="E189" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190">
+        <v>33000</v>
+      </c>
+      <c r="B190">
+        <v>2</v>
+      </c>
+      <c r="C190">
+        <v>0.1159238693482123</v>
+      </c>
+      <c r="D190">
+        <v>0.1629149838943571</v>
+      </c>
+      <c r="E190" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191">
+        <v>41000</v>
+      </c>
+      <c r="B191">
+        <v>1</v>
+      </c>
+      <c r="C191">
+        <v>-1.51904758742942</v>
+      </c>
+      <c r="D191">
+        <v>0.4650656226835881</v>
+      </c>
+      <c r="E191" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192">
+        <v>22000</v>
+      </c>
+      <c r="B192">
+        <v>2</v>
+      </c>
+      <c r="C192">
+        <v>0.4979045992645669</v>
+      </c>
+      <c r="D192">
+        <v>0.07306419333067136</v>
+      </c>
+      <c r="E192" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193">
+        <v>30000</v>
+      </c>
+      <c r="B193">
+        <v>2</v>
+      </c>
+      <c r="C193">
+        <v>-0.2660568605681423</v>
+      </c>
+      <c r="D193">
+        <v>0.2527657744580429</v>
+      </c>
+      <c r="E193" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194">
+        <v>32000</v>
+      </c>
+      <c r="B194">
+        <v>2</v>
+      </c>
+      <c r="C194">
+        <v>0.186301012054831</v>
+      </c>
+      <c r="D194">
+        <v>-0.08796902432227453</v>
+      </c>
+      <c r="E194" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195">
+        <v>25500</v>
+      </c>
+      <c r="B195">
+        <v>2</v>
+      </c>
+      <c r="C195">
+        <v>1.566618648888226</v>
+      </c>
+      <c r="D195">
+        <v>-0.3302191360690484</v>
+      </c>
+      <c r="E195" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196">
+        <v>26500</v>
+      </c>
+      <c r="B196">
+        <v>2</v>
+      </c>
+      <c r="C196">
+        <v>0.05897410208271283</v>
+      </c>
+      <c r="D196">
+        <v>-0.05801876080104597</v>
+      </c>
+      <c r="E196" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197">
+        <v>32000</v>
+      </c>
+      <c r="B197">
+        <v>2</v>
+      </c>
+      <c r="C197">
+        <v>0.05897410208271283</v>
+      </c>
+      <c r="D197">
+        <v>-0.05801876080104597</v>
+      </c>
+      <c r="E197" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198">
+        <v>25000</v>
+      </c>
+      <c r="B198">
+        <v>2</v>
+      </c>
+      <c r="C198">
+        <v>1.848321236710685</v>
+      </c>
+      <c r="D198">
+        <v>-0.3275471699984695</v>
+      </c>
+      <c r="E198" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199">
+        <v>40500</v>
+      </c>
+      <c r="B199">
+        <v>1</v>
+      </c>
+      <c r="C199">
+        <v>-2.136235758572238</v>
+      </c>
+      <c r="D199">
+        <v>0.3759130374815908</v>
+      </c>
+      <c r="E199" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200">
+        <v>29500</v>
+      </c>
+      <c r="B200">
+        <v>2</v>
+      </c>
+      <c r="C200">
+        <v>1.339013596822212</v>
+      </c>
+      <c r="D200">
+        <v>-0.2077461159135552</v>
+      </c>
+      <c r="E200" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201">
+        <v>27000</v>
+      </c>
+      <c r="B201">
+        <v>2</v>
+      </c>
+      <c r="C201">
+        <v>1.720994326738567</v>
+      </c>
+      <c r="D201">
+        <v>-0.2975969064772409</v>
+      </c>
+      <c r="E201" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202">
+        <v>33000</v>
+      </c>
+      <c r="B202">
+        <v>2</v>
+      </c>
+      <c r="C202">
+        <v>0.3406766899051717</v>
+      </c>
+      <c r="D202">
+        <v>-0.05534679473046713</v>
+      </c>
+      <c r="E202" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203">
+        <v>34000</v>
+      </c>
+      <c r="B203">
+        <v>2</v>
+      </c>
+      <c r="C203">
+        <v>0.186301012054831</v>
+      </c>
+      <c r="D203">
+        <v>-0.08796902432227453</v>
+      </c>
+      <c r="E203" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204">
+        <v>30000</v>
+      </c>
+      <c r="B204">
+        <v>2</v>
+      </c>
+      <c r="C204">
+        <v>1.975648146682803</v>
+      </c>
+      <c r="D204">
+        <v>-0.3574974335196981</v>
+      </c>
+      <c r="E204" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205">
+        <v>30000</v>
+      </c>
+      <c r="B205">
+        <v>1</v>
+      </c>
+      <c r="C205">
+        <v>-1.397739680733954</v>
+      </c>
+      <c r="D205">
+        <v>0.202201509058465</v>
+      </c>
+      <c r="E205" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206">
+        <v>27500</v>
+      </c>
+      <c r="B206">
+        <v>2</v>
+      </c>
+      <c r="C206">
+        <v>0.3136279220269492</v>
+      </c>
+      <c r="D206">
+        <v>-0.1179192878435031</v>
+      </c>
+      <c r="E206" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207">
+        <v>42500</v>
+      </c>
+      <c r="B207">
+        <v>2</v>
+      </c>
+      <c r="C207">
+        <v>0.3136279220269492</v>
+      </c>
+      <c r="D207">
+        <v>-0.1179192878435031</v>
+      </c>
+      <c r="E207" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208">
+        <v>40000</v>
+      </c>
+      <c r="B208">
+        <v>2</v>
+      </c>
+      <c r="C208">
+        <v>0.2133497799330536</v>
+      </c>
+      <c r="D208">
+        <v>-0.02539653120923854</v>
+      </c>
+      <c r="E208" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209">
+        <v>27000</v>
+      </c>
+      <c r="B209">
+        <v>2</v>
+      </c>
+      <c r="C209">
+        <v>2.357628876599158</v>
+      </c>
+      <c r="D209">
+        <v>-0.4473482240833839</v>
+      </c>
+      <c r="E209" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210">
+        <v>33000</v>
+      </c>
+      <c r="B210">
+        <v>2</v>
+      </c>
+      <c r="C210">
+        <v>0.3136279220269492</v>
+      </c>
+      <c r="D210">
+        <v>-0.1179192878435031</v>
+      </c>
+      <c r="E210" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211">
+        <v>38000</v>
+      </c>
+      <c r="B211">
+        <v>2</v>
+      </c>
+      <c r="C211">
+        <v>1.948599378804581</v>
+      </c>
+      <c r="D211">
+        <v>-0.4200699266327342</v>
+      </c>
+      <c r="E211" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212">
+        <v>30000</v>
+      </c>
+      <c r="B212">
+        <v>2</v>
+      </c>
+      <c r="C212">
+        <v>0.3406766899051717</v>
+      </c>
+      <c r="D212">
+        <v>-0.05534679473046713</v>
+      </c>
+      <c r="E212" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213">
+        <v>35000</v>
+      </c>
+      <c r="B213">
+        <v>2</v>
+      </c>
+      <c r="C213">
+        <v>-0.06835280788940534</v>
+      </c>
+      <c r="D213">
+        <v>-0.0280684972798174</v>
+      </c>
+      <c r="E213" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214">
+        <v>29000</v>
+      </c>
+      <c r="B214">
+        <v>2</v>
+      </c>
+      <c r="C214">
+        <v>0.6956086519433039</v>
+      </c>
+      <c r="D214">
+        <v>-0.2077700784071889</v>
+      </c>
+      <c r="E214" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215">
+        <v>30000</v>
+      </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+      <c r="C215">
+        <v>-1.321343534750683</v>
+      </c>
+      <c r="D215">
+        <v>0.1842313509457278</v>
+      </c>
+      <c r="E215" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216">
+        <v>31000</v>
+      </c>
+      <c r="B216">
+        <v>2</v>
+      </c>
+      <c r="C216">
+        <v>0.9502624718875402</v>
+      </c>
+      <c r="D216">
+        <v>-0.2676706054496461</v>
+      </c>
+      <c r="E216" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217">
+        <v>28500</v>
+      </c>
+      <c r="B217">
+        <v>2</v>
+      </c>
+      <c r="C217">
+        <v>0.8229355619154219</v>
+      </c>
+      <c r="D217">
+        <v>-0.2377203419284175</v>
+      </c>
+      <c r="E217" t="s">
         <v>25</v>
       </c>
     </row>
